--- a/jira_export_2026-07-20.xlsx
+++ b/jira_export_2026-07-20.xlsx
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>381 h</t>
+          <t>389 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>74.8%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -942,7 +942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P176"/>
+  <dimension ref="A1:P178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1182,7 +1182,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="15" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L6" s="15" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>1</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="L16" s="15" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>2016</v>
       </c>
       <c r="P16" s="16" t="n">
-        <v>224</v>
+        <v>217.95</v>
       </c>
     </row>
     <row r="17">
@@ -2975,12 +2975,12 @@
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33822</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[CD 29] - Installation serveurs et montée de version TEST ET PROD</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
@@ -2990,12 +2990,12 @@
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>Installation serveurs et montée de version TEST ET PROD</t>
         </is>
       </c>
       <c r="F32" s="15" t="inlineStr">
@@ -3022,37 +3022,37 @@
         <v>1</v>
       </c>
       <c r="K32" s="15" t="n">
-        <v>2.25</v>
+        <v>0.25</v>
       </c>
       <c r="L32" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33833</t>
         </is>
       </c>
       <c r="M32" s="15" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00169872</t>
         </is>
       </c>
       <c r="N32" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O32" s="16" t="n">
-        <v>219.1</v>
+        <v>0</v>
       </c>
       <c r="P32" s="16" t="n">
-        <v>97.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
@@ -3094,52 +3094,52 @@
         <v>1</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M33" s="12" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N33" s="13" t="n">
-        <v>1890</v>
-      </c>
-      <c r="O33" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O33" s="13" t="n">
+        <v>219.1</v>
       </c>
       <c r="P33" s="13" t="n">
-        <v>0</v>
+        <v>97.38</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commande modélisation supplémentaire </t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F34" s="15" t="inlineStr">
@@ -3159,64 +3159,64 @@
       </c>
       <c r="I34" s="15" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J34" s="15" t="n">
         <v>1</v>
       </c>
       <c r="K34" s="15" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="L34" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M34" s="15" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N34" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="16" t="n">
-        <v>532.4</v>
+        <v>1890</v>
+      </c>
+      <c r="O34" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P34" s="16" t="n">
-        <v>101.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33755</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MAINTENON] - Migration vers GeoDP V2</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Quentin BORDILLON</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MAINTENON</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
@@ -3226,69 +3226,69 @@
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J35" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>1.25</v>
+        <v>5.25</v>
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33764</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M35" s="12" t="inlineStr">
         <is>
-          <t>00169558</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N35" s="13" t="n">
-        <v>1365</v>
-      </c>
-      <c r="O35" s="17" t="n">
-        <v>1189.5</v>
+        <v>0</v>
+      </c>
+      <c r="O35" s="13" t="n">
+        <v>532.4</v>
       </c>
       <c r="P35" s="13" t="n">
-        <v>951.6</v>
+        <v>101.41</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33755</t>
         </is>
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[COMMUNE DE MAINTENON] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Quentin BORDILLON</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>COMMUNE DE MAINTENON</t>
         </is>
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F36" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G36" s="15" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="H36" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I36" s="15" t="inlineStr">
@@ -3310,52 +3310,52 @@
         <v>1</v>
       </c>
       <c r="K36" s="15" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L36" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33764</t>
         </is>
       </c>
       <c r="M36" s="15" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169558</t>
         </is>
       </c>
       <c r="N36" s="16" t="n">
-        <v>920</v>
+        <v>1365</v>
       </c>
       <c r="O36" s="17" t="n">
-        <v>0</v>
+        <v>1189.5</v>
       </c>
       <c r="P36" s="16" t="n">
-        <v>0</v>
+        <v>951.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33729</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
@@ -3382,22 +3382,22 @@
         <v>1</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33733</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M37" s="12" t="inlineStr">
         <is>
-          <t>00169480</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N37" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="13" t="n">
+        <v>920</v>
+      </c>
+      <c r="O37" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P37" s="13" t="n">
@@ -3407,12 +3407,12 @@
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33720</t>
+          <t>PDMDEP-33729</t>
         </is>
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LEVALLOIS PERRET] - PRESTA PURGE DES ACTES EN URGENCE</t>
+          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
         </is>
       </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
-          <t>PRESTA PURGE DES ACTES EN URGENCE</t>
+          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="F38" s="15" t="inlineStr">
@@ -3458,18 +3458,18 @@
       </c>
       <c r="L38" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33724</t>
+          <t>PDMDEP-33733</t>
         </is>
       </c>
       <c r="M38" s="15" t="inlineStr">
         <is>
-          <t>00169462</t>
+          <t>00169480</t>
         </is>
       </c>
       <c r="N38" s="16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O38" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P38" s="16" t="n">
@@ -3479,32 +3479,32 @@
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33686</t>
+          <t>PDMDEP-33720</t>
         </is>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>[EUROMETROPOLE DE METZ] - Paiement CB + 3 PAX</t>
+          <t>[COMMUNE DE LEVALLOIS PERRET] - PRESTA PURGE DES ACTES EN URGENCE</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>EUROMETROPOLE DE METZ</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Paiement CB + 3 PAX</t>
+          <t>PRESTA PURGE DES ACTES EN URGENCE</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G39" s="12" t="inlineStr">
@@ -3519,29 +3519,29 @@
       </c>
       <c r="I39" s="12" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J39" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L39" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33694</t>
+          <t>PDMDEP-33724</t>
         </is>
       </c>
       <c r="M39" s="12" t="inlineStr">
         <is>
-          <t>00169321</t>
+          <t>00169462</t>
         </is>
       </c>
       <c r="N39" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O39" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P39" s="13" t="n">
@@ -3551,27 +3551,27 @@
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33610</t>
+          <t>PDMDEP-33686</t>
         </is>
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MORLAIX] - MIGRATION GEODP PLACIER hors matériel </t>
+          <t>[EUROMETROPOLE DE METZ] - Paiement CB + 3 PAX</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>Quentin BORDILLON</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MORLAIX</t>
+          <t>EUROMETROPOLE DE METZ</t>
         </is>
       </c>
       <c r="E40" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
+          <t>Paiement CB + 3 PAX</t>
         </is>
       </c>
       <c r="F40" s="15" t="inlineStr">
@@ -3586,64 +3586,64 @@
       </c>
       <c r="H40" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I40" s="15" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="J40" s="15" t="n">
         <v>1</v>
       </c>
       <c r="K40" s="15" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L40" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33616</t>
+          <t>PDMDEP-33694</t>
         </is>
       </c>
       <c r="M40" s="15" t="inlineStr">
         <is>
-          <t>00169015</t>
+          <t>00169321</t>
         </is>
       </c>
       <c r="N40" s="16" t="n">
-        <v>4040</v>
-      </c>
-      <c r="O40" s="17" t="n">
-        <v>1010</v>
+        <v>0</v>
+      </c>
+      <c r="O40" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P40" s="16" t="n">
-        <v>1346.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33610</t>
         </is>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">[COMMUNE DE MORLAIX] - MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Quentin BORDILLON</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>COMMUNE DE MORLAIX</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I41" s="12" t="inlineStr">
@@ -3670,57 +3670,57 @@
         <v>1</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33616</t>
         </is>
       </c>
       <c r="M41" s="12" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00169015</t>
         </is>
       </c>
       <c r="N41" s="13" t="n">
-        <v>407</v>
+        <v>4040</v>
       </c>
       <c r="O41" s="17" t="n">
-        <v>203.5</v>
+        <v>1010</v>
       </c>
       <c r="P41" s="13" t="n">
-        <v>135.67</v>
+        <v>1346.67</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33566</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LILLE] Flux WFS</t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
-          <t>MM - Up - LiExp - Flux WFS (PS)</t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F42" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G42" s="15" t="inlineStr">
@@ -3735,64 +3735,64 @@
       </c>
       <c r="I42" s="15" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J42" s="15" t="n">
         <v>1</v>
       </c>
       <c r="K42" s="15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L42" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33570</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M42" s="15" t="inlineStr">
         <is>
-          <t>00168466</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N42" s="16" t="n">
-        <v>895</v>
+        <v>407</v>
       </c>
       <c r="O42" s="17" t="n">
-        <v>0</v>
+        <v>203.5</v>
       </c>
       <c r="P42" s="16" t="n">
-        <v>0</v>
+        <v>135.67</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33553</t>
+          <t>PDMDEP-33566</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - MM - Up - GeODP - PAX</t>
+          <t>[COMMUNE DE LILLE] Flux WFS</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>MM - Up - GeODP - PAX</t>
+          <t>MM - Up - LiExp - Flux WFS (PS)</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G43" s="12" t="inlineStr">
@@ -3818,16 +3818,16 @@
       </c>
       <c r="L43" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33561</t>
+          <t>PDMDEP-33570</t>
         </is>
       </c>
       <c r="M43" s="12" t="inlineStr">
         <is>
-          <t>00168460</t>
+          <t>00168466</t>
         </is>
       </c>
       <c r="N43" s="13" t="n">
-        <v>500</v>
+        <v>895</v>
       </c>
       <c r="O43" s="17" t="n">
         <v>0</v>
@@ -3839,12 +3839,12 @@
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33517</t>
+          <t>PDMDEP-33553</t>
         </is>
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - MM - Up - GeODP - PAX</t>
         </is>
       </c>
       <c r="C44" s="15" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE MONTREUIL</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
-          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>MM - Up - GeODP - PAX</t>
         </is>
       </c>
       <c r="F44" s="15" t="inlineStr">
@@ -3874,32 +3874,32 @@
       </c>
       <c r="H44" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I44" s="15" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="J44" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K44" s="15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="L44" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33526</t>
+          <t>PDMDEP-33561</t>
         </is>
       </c>
       <c r="M44" s="15" t="inlineStr">
         <is>
-          <t>00168179</t>
+          <t>00168460</t>
         </is>
       </c>
       <c r="N44" s="16" t="n">
-        <v>1416</v>
+        <v>500</v>
       </c>
       <c r="O44" s="17" t="n">
         <v>0</v>
@@ -3911,27 +3911,27 @@
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33500</t>
+          <t>PDMDEP-33517</t>
         </is>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
+          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mairie de Carcès </t>
+          <t>VILLE DE MONTREUIL</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
+          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
@@ -3958,57 +3958,57 @@
         <v>2</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>4</v>
+        <v>1.75</v>
       </c>
       <c r="L45" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33509</t>
+          <t>PDMDEP-33526</t>
         </is>
       </c>
       <c r="M45" s="12" t="inlineStr">
         <is>
-          <t>00168117</t>
+          <t>00168179</t>
         </is>
       </c>
       <c r="N45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="13" t="n">
-        <v>732.6</v>
+        <v>1416</v>
+      </c>
+      <c r="O45" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P45" s="13" t="n">
-        <v>183.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33500</t>
         </is>
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t xml:space="preserve">Mairie de Carcès </t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="F46" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G46" s="15" t="inlineStr">
@@ -4018,69 +4018,69 @@
       </c>
       <c r="H46" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J46" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K46" s="15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L46" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33509</t>
         </is>
       </c>
       <c r="M46" s="15" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00168117</t>
         </is>
       </c>
       <c r="N46" s="16" t="n">
-        <v>171.4</v>
-      </c>
-      <c r="O46" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O46" s="16" t="n">
+        <v>732.6</v>
       </c>
       <c r="P46" s="16" t="n">
-        <v>0</v>
+        <v>183.15</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33461</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>[Mairie de Buis-les-baronnies] - INITIATION GEODP</t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Mairie de Buis-les-baronnies</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>INITIATION GEODP</t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G47" s="12" t="inlineStr">
@@ -4106,16 +4106,16 @@
       </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33465</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M47" s="12" t="inlineStr">
         <is>
-          <t>00167986</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N47" s="13" t="n">
-        <v>450</v>
+        <v>171.4</v>
       </c>
       <c r="O47" s="17" t="n">
         <v>0</v>
@@ -4127,32 +4127,32 @@
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33451</t>
+          <t>PDMDEP-33461</t>
         </is>
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>[VILLE DE CHATELLERAULT] - FDS pour Littéralis Expert</t>
+          <t>[Mairie de Buis-les-baronnies] - INITIATION GEODP</t>
         </is>
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE CHATELLERAULT</t>
+          <t>Mairie de Buis-les-baronnies</t>
         </is>
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t>FDS pour Littéralis Expert</t>
+          <t>INITIATION GEODP</t>
         </is>
       </c>
       <c r="F48" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G48" s="15" t="inlineStr">
@@ -4174,22 +4174,22 @@
         <v>2</v>
       </c>
       <c r="K48" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L48" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33455</t>
+          <t>PDMDEP-33465</t>
         </is>
       </c>
       <c r="M48" s="15" t="inlineStr">
         <is>
-          <t>00167958</t>
+          <t>00167986</t>
         </is>
       </c>
       <c r="N48" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="16" t="n">
+        <v>450</v>
+      </c>
+      <c r="O48" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P48" s="16" t="n">
@@ -4199,32 +4199,32 @@
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33451</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES ] - Migration multi-modules (hors taxi) </t>
+          <t>[VILLE DE CHATELLERAULT] - FDS pour Littéralis Expert</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t>VILLE DE CHATELLERAULT</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t>FDS pour Littéralis Expert</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G49" s="12" t="inlineStr">
@@ -4234,64 +4234,64 @@
       </c>
       <c r="H49" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I49" s="12" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J49" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>1.75</v>
+        <v>0.25</v>
       </c>
       <c r="L49" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33455</t>
         </is>
       </c>
       <c r="M49" s="12" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00167958</t>
         </is>
       </c>
       <c r="N49" s="13" t="n">
-        <v>417.4</v>
+        <v>0</v>
       </c>
       <c r="O49" s="13" t="n">
-        <v>1252.2</v>
+        <v>0</v>
       </c>
       <c r="P49" s="13" t="n">
-        <v>715.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33408</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Flayosc] - Migration 3 activités GEODP 1 vers GEODP 2</t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES ] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>Commune de Flayosc</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>Migration 3 activités GEODP 1 vers GEODP 2</t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F50" s="15" t="inlineStr">
@@ -4318,57 +4318,57 @@
         <v>2</v>
       </c>
       <c r="K50" s="15" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="L50" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33415</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M50" s="15" t="inlineStr">
         <is>
-          <t>00167809</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N50" s="16" t="n">
-        <v>0</v>
+        <v>417.4</v>
       </c>
       <c r="O50" s="16" t="n">
-        <v>203</v>
+        <v>1252.2</v>
       </c>
       <c r="P50" s="16" t="n">
-        <v>81.2</v>
+        <v>715.54</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33386</t>
+          <t>PDMDEP-33408</t>
         </is>
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
+          <t>[Commune de Flayosc] - Migration 3 activités GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
+          <t>Commune de Flayosc</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prestation modélisation Littéralis </t>
+          <t>Migration 3 activités GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G51" s="12" t="inlineStr">
@@ -4378,49 +4378,49 @@
       </c>
       <c r="H51" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I51" s="12" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J51" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="L51" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33390</t>
+          <t>PDMDEP-33415</t>
         </is>
       </c>
       <c r="M51" s="12" t="inlineStr">
         <is>
-          <t>00167823</t>
+          <t>00167809</t>
         </is>
       </c>
       <c r="N51" s="13" t="n">
-        <v>617.04</v>
+        <v>0</v>
       </c>
       <c r="O51" s="13" t="n">
-        <v>1028.4</v>
+        <v>203</v>
       </c>
       <c r="P51" s="13" t="n">
-        <v>342.8</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33363</t>
+          <t>PDMDEP-33386</t>
         </is>
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>[AMIENS METROPOLE] LiExp - Vérif</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="C52" s="15" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>AMIENS METROPOLE</t>
+          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
         </is>
       </c>
       <c r="E52" s="15" t="inlineStr">
         <is>
-          <t>MM - Up - LiExp - Vérif</t>
+          <t xml:space="preserve">Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="F52" s="15" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G52" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H52" s="15" t="inlineStr">
@@ -4455,36 +4455,44 @@
       </c>
       <c r="I52" s="15" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J52" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K52" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L52" s="15" t="inlineStr"/>
-      <c r="M52" s="15" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L52" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33390</t>
+        </is>
+      </c>
+      <c r="M52" s="15" t="inlineStr">
+        <is>
+          <t>00167823</t>
+        </is>
+      </c>
       <c r="N52" s="16" t="n">
-        <v>0</v>
+        <v>617.04</v>
       </c>
       <c r="O52" s="16" t="n">
-        <v>0</v>
+        <v>1028.4</v>
       </c>
       <c r="P52" s="16" t="n">
-        <v>0</v>
+        <v>342.8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33348</t>
+          <t>PDMDEP-33363</t>
         </is>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[MAISONS ALFORT] - Modélisation + Modif Marianne </t>
+          <t>[AMIENS METROPOLE] LiExp - Vérif</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
@@ -4494,12 +4502,12 @@
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE MAISONS ALFORT </t>
+          <t>AMIENS METROPOLE</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modélisation + Modif Marianne </t>
+          <t>MM - Up - LiExp - Vérif</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
@@ -4509,7 +4517,7 @@
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H53" s="12" t="inlineStr">
@@ -4519,29 +4527,21 @@
       </c>
       <c r="I53" s="12" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="J53" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-33352</t>
-        </is>
-      </c>
-      <c r="M53" s="12" t="inlineStr">
-        <is>
-          <t>00167402</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L53" s="12" t="inlineStr"/>
+      <c r="M53" s="12" t="inlineStr"/>
       <c r="N53" s="13" t="n">
-        <v>171.4</v>
-      </c>
-      <c r="O53" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P53" s="13" t="n">
@@ -4551,32 +4551,32 @@
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33348</t>
         </is>
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t xml:space="preserve">[MAISONS ALFORT] - Modélisation + Modif Marianne </t>
         </is>
       </c>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t xml:space="preserve">COMMUNE DE MAISONS ALFORT </t>
         </is>
       </c>
       <c r="E54" s="15" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t xml:space="preserve">Modélisation + Modif Marianne </t>
         </is>
       </c>
       <c r="F54" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G54" s="15" t="inlineStr">
@@ -4586,12 +4586,12 @@
       </c>
       <c r="H54" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="J54" s="15" t="n">
@@ -4602,19 +4602,19 @@
       </c>
       <c r="L54" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33352</t>
         </is>
       </c>
       <c r="M54" s="15" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00167402</t>
         </is>
       </c>
       <c r="N54" s="16" t="n">
-        <v>149</v>
-      </c>
-      <c r="O54" s="16" t="n">
-        <v>149</v>
+        <v>171.4</v>
+      </c>
+      <c r="O54" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P54" s="16" t="n">
         <v>0</v>
@@ -4623,32 +4623,32 @@
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G55" s="12" t="inlineStr">
@@ -4658,35 +4658,35 @@
       </c>
       <c r="H55" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I55" s="12" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J55" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L55" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M55" s="12" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N55" s="13" t="n">
-        <v>625</v>
-      </c>
-      <c r="O55" s="17" t="n">
-        <v>0</v>
+        <v>149</v>
+      </c>
+      <c r="O55" s="13" t="n">
+        <v>149</v>
       </c>
       <c r="P55" s="13" t="n">
         <v>0</v>
@@ -4746,48 +4746,48 @@
       </c>
       <c r="L56" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M56" s="15" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N56" s="16" t="n">
-        <v>600</v>
+        <v>625</v>
       </c>
       <c r="O56" s="17" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="P56" s="16" t="n">
-        <v>896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33203</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>[CD 38] - LiExp - Crédits d'heure + TDC MV</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>LiExp - Crédits d'heure + TDC MV</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="I57" s="12" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J57" s="12" t="n">
@@ -4818,53 +4818,53 @@
       </c>
       <c r="L57" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33207</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M57" s="12" t="inlineStr">
         <is>
-          <t>00166553</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N57" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="13" t="n">
-        <v>0</v>
+        <v>600</v>
+      </c>
+      <c r="O57" s="17" t="n">
+        <v>224</v>
       </c>
       <c r="P57" s="13" t="n">
-        <v>0</v>
+        <v>896</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33203</t>
         </is>
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[CD 38] - LiExp - Crédits d'heure + TDC MV</t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E58" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>LiExp - Crédits d'heure + TDC MV</t>
         </is>
       </c>
       <c r="F58" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G58" s="15" t="inlineStr">
@@ -4874,64 +4874,64 @@
       </c>
       <c r="H58" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="J58" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K58" s="15" t="n">
-        <v>6.5</v>
+        <v>0.25</v>
       </c>
       <c r="L58" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33207</t>
         </is>
       </c>
       <c r="M58" s="15" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166553</t>
         </is>
       </c>
       <c r="N58" s="16" t="n">
-        <v>3621</v>
+        <v>0</v>
       </c>
       <c r="O58" s="16" t="n">
-        <v>4224.5</v>
+        <v>0</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>649.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33012</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRASSE</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
@@ -4951,64 +4951,64 @@
       </c>
       <c r="I59" s="12" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J59" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="L59" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33021</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M59" s="12" t="inlineStr">
         <is>
-          <t>00165368</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N59" s="13" t="n">
-        <v>1618.5</v>
+        <v>3621</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>1996.15</v>
+        <v>4224.5</v>
       </c>
       <c r="P59" s="13" t="n">
-        <v>499.04</v>
+        <v>649.92</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33012</t>
         </is>
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE GRASSE</t>
         </is>
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="F60" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G60" s="15" t="inlineStr">
@@ -5018,69 +5018,69 @@
       </c>
       <c r="H60" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J60" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K60" s="15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L60" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33021</t>
         </is>
       </c>
       <c r="M60" s="15" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165368</t>
         </is>
       </c>
       <c r="N60" s="16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O60" s="17" t="n">
-        <v>0</v>
+        <v>1618.5</v>
+      </c>
+      <c r="O60" s="16" t="n">
+        <v>1996.15</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>0</v>
+        <v>499.04</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G61" s="12" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="H61" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I61" s="12" t="inlineStr">
@@ -5102,22 +5102,22 @@
         <v>3</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L61" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M61" s="12" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N61" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O61" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P61" s="13" t="n">
@@ -5127,27 +5127,27 @@
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32902</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE BALARUC-LES-BAINS ] - COMMANDE PAX </t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE BALARUCL-LES-BAINS </t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E62" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMANDE PAX </t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F62" s="15" t="inlineStr">
@@ -5162,12 +5162,12 @@
       </c>
       <c r="H62" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J62" s="15" t="n">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="L62" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32910</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M62" s="15" t="inlineStr">
         <is>
-          <t>00159637</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N62" s="16" t="n">
@@ -5199,27 +5199,27 @@
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32860</t>
+          <t>PDMDEP-32902</t>
         </is>
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LE LUC EN PROVENCE] - MIGRATION SIMPLE GEODP PLACIER</t>
+          <t xml:space="preserve">[COMMUNE DE BALARUC-LES-BAINS ] - COMMANDE PAX </t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LE LUC EN PROVENCE</t>
+          <t xml:space="preserve">COMMUNE DE BALARUCL-LES-BAINS </t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>MIGRATION SIMPLE GEODP PLACIER</t>
+          <t xml:space="preserve">COMMANDE PAX </t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
@@ -5234,35 +5234,35 @@
       </c>
       <c r="H63" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I63" s="12" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="J63" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L63" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32869</t>
+          <t>PDMDEP-32910</t>
         </is>
       </c>
       <c r="M63" s="12" t="inlineStr">
         <is>
-          <t>00164607</t>
+          <t>00159637</t>
         </is>
       </c>
       <c r="N63" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="P63" s="13" t="n">
         <v>0</v>
@@ -5271,27 +5271,27 @@
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32848</t>
+          <t>PDMDEP-32860</t>
         </is>
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRENOBLE] - Modification modèles de facture</t>
+          <t>[COMMUNE DE LE LUC EN PROVENCE] - MIGRATION SIMPLE GEODP PLACIER</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRENOBLE</t>
+          <t>COMMUNE DE LE LUC EN PROVENCE</t>
         </is>
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t>Modification modèles de facture</t>
+          <t>MIGRATION SIMPLE GEODP PLACIER</t>
         </is>
       </c>
       <c r="F64" s="15" t="inlineStr">
@@ -5306,12 +5306,12 @@
       </c>
       <c r="H64" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="J64" s="15" t="n">
@@ -5322,19 +5322,19 @@
       </c>
       <c r="L64" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32852</t>
+          <t>PDMDEP-32869</t>
         </is>
       </c>
       <c r="M64" s="15" t="inlineStr">
         <is>
-          <t>00164564</t>
+          <t>00164607</t>
         </is>
       </c>
       <c r="N64" s="16" t="n">
-        <v>300</v>
-      </c>
-      <c r="O64" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O64" s="16" t="n">
+        <v>245</v>
       </c>
       <c r="P64" s="16" t="n">
         <v>0</v>
@@ -5343,12 +5343,12 @@
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32831</t>
+          <t>PDMDEP-32848</t>
         </is>
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE PANTIN] - Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+          <t>[COMMUNE DE GRENOBLE] - Modification modèles de facture</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE PANTIN</t>
+          <t>COMMUNE DE GRENOBLE</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+          <t>Modification modèles de facture</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="I65" s="12" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="J65" s="12" t="n">
@@ -5394,16 +5394,16 @@
       </c>
       <c r="L65" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32837</t>
+          <t>PDMDEP-32852</t>
         </is>
       </c>
       <c r="M65" s="12" t="inlineStr">
         <is>
-          <t>00164275</t>
+          <t>00164564</t>
         </is>
       </c>
       <c r="N65" s="13" t="n">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="O65" s="17" t="n">
         <v>0</v>
@@ -5415,32 +5415,32 @@
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32831</t>
         </is>
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[COMMUNE DE PANTIN] - Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE DE PANTIN</t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
         </is>
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G66" s="15" t="inlineStr">
@@ -5455,44 +5455,44 @@
       </c>
       <c r="I66" s="15" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="J66" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K66" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L66" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32837</t>
         </is>
       </c>
       <c r="M66" s="15" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00164275</t>
         </is>
       </c>
       <c r="N66" s="16" t="n">
-        <v>705</v>
-      </c>
-      <c r="O66" s="16" t="n">
-        <v>1057.5</v>
+        <v>900</v>
+      </c>
+      <c r="O66" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P66" s="16" t="n">
-        <v>528.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32759</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE DU GRAND REIMS - DSIT] - MV app/ infra + màj carto</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE DU GRAND REIMS - DSIT</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr">
@@ -5534,57 +5534,57 @@
         <v>3</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L67" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32763</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M67" s="12" t="inlineStr">
         <is>
-          <t>00163805</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N67" s="13" t="n">
-        <v>564</v>
+        <v>705</v>
       </c>
       <c r="O67" s="13" t="n">
-        <v>705</v>
+        <v>1057.5</v>
       </c>
       <c r="P67" s="13" t="n">
-        <v>0</v>
+        <v>528.75</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32732</t>
+          <t>PDMDEP-32759</t>
         </is>
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
+          <t>[COMMUNAUTE URBAINE DU GRAND REIMS - DSIT] - MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA SENTINELLE</t>
+          <t>COMMUNAUTE URBAINE DU GRAND REIMS - DSIT</t>
         </is>
       </c>
       <c r="E68" s="15" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Caisse</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G68" s="15" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="H68" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I68" s="15" t="inlineStr">
@@ -5606,37 +5606,37 @@
         <v>3</v>
       </c>
       <c r="K68" s="15" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32741</t>
+          <t>PDMDEP-32763</t>
         </is>
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>00163789</t>
+          <t>00163805</t>
         </is>
       </c>
       <c r="N68" s="16" t="n">
-        <v>2138.2</v>
-      </c>
-      <c r="O68" s="17" t="n">
-        <v>1375.2</v>
+        <v>564</v>
+      </c>
+      <c r="O68" s="16" t="n">
+        <v>705</v>
       </c>
       <c r="P68" s="16" t="n">
-        <v>305.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32703</t>
+          <t>PDMDEP-32732</t>
         </is>
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[MAIRIE DE MIRIBEL] - MIGRATION PLACIER SIMPLE + PAX </t>
+          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MIRIBEL</t>
+          <t>MAIRIE DE LA SENTINELLE</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION PLACIER SIMPLE + PAX </t>
+          <t>Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
@@ -5666,69 +5666,69 @@
       </c>
       <c r="H69" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I69" s="12" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J69" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L69" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32712</t>
+          <t>PDMDEP-32741</t>
         </is>
       </c>
       <c r="M69" s="12" t="inlineStr">
         <is>
-          <t>00163498</t>
+          <t>00163789</t>
         </is>
       </c>
       <c r="N69" s="13" t="n">
-        <v>283.5</v>
+        <v>2138.2</v>
       </c>
       <c r="O69" s="17" t="n">
-        <v>0</v>
+        <v>1375.2</v>
       </c>
       <c r="P69" s="13" t="n">
-        <v>0</v>
+        <v>305.6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32703</t>
         </is>
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t xml:space="preserve">[MAIRIE DE MIRIBEL] - MIGRATION PLACIER SIMPLE + PAX </t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>MAIRIE DE MIRIBEL</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">MIGRATION PLACIER SIMPLE + PAX </t>
         </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G70" s="15" t="inlineStr">
@@ -5738,32 +5738,32 @@
       </c>
       <c r="H70" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I70" s="15" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="J70" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K70" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L70" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32712</t>
         </is>
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00163498</t>
         </is>
       </c>
       <c r="N70" s="16" t="n">
-        <v>548.4</v>
+        <v>283.5</v>
       </c>
       <c r="O70" s="17" t="n">
         <v>0</v>
@@ -5775,32 +5775,32 @@
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32598</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Déploiement GeoDP Caisse</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G71" s="12" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="H71" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I71" s="12" t="inlineStr">
@@ -5822,20 +5822,20 @@
         <v>3</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32607</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M71" s="12" t="inlineStr">
         <is>
-          <t>00163155</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N71" s="13" t="n">
-        <v>552</v>
+        <v>548.4</v>
       </c>
       <c r="O71" s="17" t="n">
         <v>0</v>
@@ -5847,32 +5847,32 @@
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32598</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G72" s="15" t="inlineStr">
@@ -5882,69 +5882,69 @@
       </c>
       <c r="H72" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I72" s="15" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J72" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K72" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32607</t>
         </is>
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163155</t>
         </is>
       </c>
       <c r="N72" s="16" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O72" s="16" t="n">
-        <v>142.1</v>
+        <v>552</v>
+      </c>
+      <c r="O72" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P72" s="16" t="n">
-        <v>142.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G73" s="12" t="inlineStr">
@@ -5954,69 +5954,69 @@
       </c>
       <c r="H73" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I73" s="12" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J73" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L73" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M73" s="12" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N73" s="13" t="n">
-        <v>1868</v>
-      </c>
-      <c r="O73" s="17" t="n">
-        <v>0</v>
+        <v>142.1</v>
+      </c>
+      <c r="O73" s="13" t="n">
+        <v>142.1</v>
       </c>
       <c r="P73" s="13" t="n">
-        <v>0</v>
+        <v>142.1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod </t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G74" s="15" t="inlineStr">
@@ -6026,32 +6026,32 @@
       </c>
       <c r="H74" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I74" s="15" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J74" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K74" s="15" t="n">
-        <v>0.25</v>
+        <v>4</v>
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N74" s="16" t="n">
-        <v>882.5</v>
+        <v>1868</v>
       </c>
       <c r="O74" s="17" t="n">
         <v>0</v>
@@ -6063,27 +6063,27 @@
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32400</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t xml:space="preserve">[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
@@ -6103,29 +6103,29 @@
       </c>
       <c r="I75" s="12" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J75" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>1.25</v>
+        <v>0.25</v>
       </c>
       <c r="L75" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32406</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M75" s="12" t="inlineStr">
         <is>
-          <t>00161680</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N75" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" s="13" t="n">
+        <v>882.5</v>
+      </c>
+      <c r="O75" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P75" s="13" t="n">
@@ -6135,32 +6135,32 @@
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32400</t>
         </is>
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G76" s="15" t="inlineStr">
@@ -6170,35 +6170,35 @@
       </c>
       <c r="H76" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J76" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K76" s="15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32406</t>
         </is>
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161680</t>
         </is>
       </c>
       <c r="N76" s="16" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="O76" s="16" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="P76" s="16" t="n">
         <v>0</v>
@@ -6207,32 +6207,32 @@
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G77" s="12" t="inlineStr">
@@ -6242,69 +6242,69 @@
       </c>
       <c r="H77" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I77" s="12" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J77" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="L77" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M77" s="12" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N77" s="13" t="n">
-        <v>1046.5</v>
-      </c>
-      <c r="O77" s="17" t="n">
-        <v>637</v>
+        <v>450</v>
+      </c>
+      <c r="O77" s="13" t="n">
+        <v>450</v>
       </c>
       <c r="P77" s="13" t="n">
-        <v>74.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32152</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G78" s="15" t="inlineStr">
@@ -6314,64 +6314,64 @@
       </c>
       <c r="H78" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J78" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K78" s="15" t="n">
-        <v>3.25</v>
+        <v>8.5</v>
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32161</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>00160661</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N78" s="16" t="n">
-        <v>765</v>
-      </c>
-      <c r="O78" s="16" t="n">
-        <v>892.5</v>
+        <v>1046.5</v>
+      </c>
+      <c r="O78" s="17" t="n">
+        <v>637</v>
       </c>
       <c r="P78" s="16" t="n">
-        <v>274.62</v>
+        <v>74.94</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32152</t>
         </is>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
@@ -6398,52 +6398,52 @@
         <v>4</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>1.25</v>
+        <v>3.25</v>
       </c>
       <c r="L79" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32161</t>
         </is>
       </c>
       <c r="M79" s="12" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160661</t>
         </is>
       </c>
       <c r="N79" s="13" t="n">
-        <v>0</v>
+        <v>765</v>
       </c>
       <c r="O79" s="13" t="n">
-        <v>300</v>
+        <v>892.5</v>
       </c>
       <c r="P79" s="13" t="n">
-        <v>240</v>
+        <v>274.62</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
@@ -6458,49 +6458,49 @@
       </c>
       <c r="H80" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I80" s="15" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J80" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K80" s="15" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="L80" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M80" s="15" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N80" s="16" t="n">
-        <v>407</v>
-      </c>
-      <c r="O80" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O80" s="16" t="n">
+        <v>300</v>
       </c>
       <c r="P80" s="16" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
@@ -6530,32 +6530,32 @@
       </c>
       <c r="H81" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I81" s="12" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J81" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L81" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M81" s="12" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N81" s="13" t="n">
-        <v>257.15</v>
+        <v>407</v>
       </c>
       <c r="O81" s="17" t="n">
         <v>0</v>
@@ -6567,32 +6567,32 @@
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F82" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G82" s="15" t="inlineStr">
@@ -6602,32 +6602,32 @@
       </c>
       <c r="H82" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I82" s="15" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J82" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K82" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L82" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M82" s="15" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N82" s="16" t="n">
-        <v>440.38</v>
+        <v>257.15</v>
       </c>
       <c r="O82" s="17" t="n">
         <v>0</v>
@@ -6639,32 +6639,32 @@
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G83" s="12" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="H83" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I83" s="12" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J83" s="12" t="n">
@@ -6690,16 +6690,16 @@
       </c>
       <c r="L83" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M83" s="12" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N83" s="13" t="n">
-        <v>285</v>
+        <v>440.38</v>
       </c>
       <c r="O83" s="17" t="n">
         <v>0</v>
@@ -6711,32 +6711,32 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G84" s="15" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="I84" s="15" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J84" s="15" t="n">
@@ -6762,19 +6762,19 @@
       </c>
       <c r="L84" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M84" s="15" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N84" s="16" t="n">
-        <v>120</v>
-      </c>
-      <c r="O84" s="16" t="n">
-        <v>120</v>
+        <v>285</v>
+      </c>
+      <c r="O84" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P84" s="16" t="n">
         <v>0</v>
@@ -6783,32 +6783,32 @@
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31938</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- GeODP tous modules - intégration en masse n° tiers</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>GeODP tous modules - intégration en masse n° tiers</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G85" s="12" t="inlineStr">
@@ -6834,19 +6834,19 @@
       </c>
       <c r="L85" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31942</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M85" s="12" t="inlineStr">
         <is>
-          <t>00159717</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N85" s="13" t="n">
-        <v>45</v>
-      </c>
-      <c r="O85" s="17" t="n">
-        <v>0</v>
+        <v>120</v>
+      </c>
+      <c r="O85" s="13" t="n">
+        <v>120</v>
       </c>
       <c r="P85" s="13" t="n">
         <v>0</v>
@@ -6855,27 +6855,27 @@
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31938</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>METROPOLE TOULON- GeODP tous modules - intégration en masse n° tiers</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E86" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>GeODP tous modules - intégration en masse n° tiers</t>
         </is>
       </c>
       <c r="F86" s="15" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="H86" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I86" s="15" t="inlineStr">
@@ -6906,19 +6906,19 @@
       </c>
       <c r="L86" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31942</t>
         </is>
       </c>
       <c r="M86" s="15" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159717</t>
         </is>
       </c>
       <c r="N86" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" s="16" t="n">
-        <v>367.5</v>
+        <v>45</v>
+      </c>
+      <c r="O86" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P86" s="16" t="n">
         <v>0</v>
@@ -6927,12 +6927,12 @@
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
@@ -6967,59 +6967,59 @@
       </c>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J87" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31821</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M87" s="12" t="inlineStr">
         <is>
-          <t>00159471</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N87" s="13" t="n">
-        <v>420</v>
-      </c>
-      <c r="O87" s="17" t="n">
-        <v>210</v>
+        <v>0</v>
+      </c>
+      <c r="O87" s="13" t="n">
+        <v>367.5</v>
       </c>
       <c r="P87" s="13" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E88" s="15" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F88" s="15" t="inlineStr">
@@ -7034,49 +7034,49 @@
       </c>
       <c r="H88" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J88" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K88" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M88" s="15" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N88" s="16" t="n">
-        <v>203.5</v>
+        <v>420</v>
       </c>
       <c r="O88" s="17" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="P88" s="16" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
@@ -7086,12 +7086,12 @@
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
@@ -7106,34 +7106,34 @@
       </c>
       <c r="H89" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J89" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K89" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M89" s="12" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N89" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" s="13" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="O89" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P89" s="13" t="n">
@@ -7143,32 +7143,32 @@
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E90" s="15" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F90" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G90" s="15" t="inlineStr">
@@ -7178,64 +7178,64 @@
       </c>
       <c r="H90" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J90" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K90" s="15" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L90" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M90" s="15" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N90" s="16" t="n">
-        <v>1500</v>
-      </c>
-      <c r="O90" s="17" t="n">
-        <v>214.9</v>
+        <v>0</v>
+      </c>
+      <c r="O90" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P90" s="16" t="n">
-        <v>143.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31516</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>[VIRE NORMANDIE] - Litteralis Verif</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIRE NORMANDIE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Litteralis Verif</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H91" s="12" t="inlineStr">
@@ -7262,82 +7262,82 @@
         <v>5</v>
       </c>
       <c r="K91" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L91" s="12" t="inlineStr"/>
-      <c r="M91" s="12" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L91" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-31546</t>
+        </is>
+      </c>
+      <c r="M91" s="12" t="inlineStr">
+        <is>
+          <t>00157816</t>
+        </is>
+      </c>
       <c r="N91" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" s="13" t="n">
-        <v>0</v>
+        <v>1500</v>
+      </c>
+      <c r="O91" s="17" t="n">
+        <v>214.9</v>
       </c>
       <c r="P91" s="13" t="n">
-        <v>0</v>
+        <v>143.27</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-31516</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 [RETOUR COMMERCE SANS REPONSE DU CLIENT]</t>
+          <t>[VIRE NORMANDIE] - Litteralis Verif</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>COMMUNE DE VIRE NORMANDIE</t>
         </is>
       </c>
       <c r="E92" s="15" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Litteralis Verif</t>
         </is>
       </c>
       <c r="F92" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G92" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H92" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J92" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K92" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L92" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-31488</t>
-        </is>
-      </c>
-      <c r="M92" s="15" t="inlineStr">
-        <is>
-          <t>00157472</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L92" s="15" t="inlineStr"/>
+      <c r="M92" s="15" t="inlineStr"/>
       <c r="N92" s="16" t="n">
         <v>0</v>
       </c>
@@ -7351,32 +7351,32 @@
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31479</t>
         </is>
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 [RETOUR COMMERCE SANS REPONSE DU CLIENT]</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE TREGUIER</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F93" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G93" s="12" t="inlineStr">
@@ -7386,28 +7386,28 @@
       </c>
       <c r="H93" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I93" s="12" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="J93" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L93" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31468</t>
+          <t>PDMDEP-31488</t>
         </is>
       </c>
       <c r="M93" s="12" t="inlineStr">
         <is>
-          <t>00157346</t>
+          <t>00157472</t>
         </is>
       </c>
       <c r="N93" s="13" t="n">
@@ -7423,32 +7423,32 @@
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E94" s="15" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G94" s="15" t="inlineStr">
@@ -7458,34 +7458,34 @@
       </c>
       <c r="H94" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J94" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K94" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M94" s="15" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N94" s="16" t="n">
-        <v>210</v>
-      </c>
-      <c r="O94" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P94" s="16" t="n">
@@ -7495,27 +7495,27 @@
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31340</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE DINARD] - Ajout module caisse parking / Ajout export finance pour module placier </t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Flavie BARDIN</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE DINARD</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout module caisse parking / Ajout export finance pour module placier </t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="H95" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I95" s="12" t="inlineStr">
@@ -7542,22 +7542,22 @@
         <v>5</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L95" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31346</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M95" s="12" t="inlineStr">
         <is>
-          <t>00157037</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N95" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" s="13" t="n">
+        <v>210</v>
+      </c>
+      <c r="O95" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P95" s="13" t="n">
@@ -7567,32 +7567,32 @@
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31269</t>
+          <t>PDMDEP-31340</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - Crédit d'heures</t>
+          <t xml:space="preserve">[COMMUNE DE DINARD] - Ajout module caisse parking / Ajout export finance pour module placier </t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Flavie BARDIN</t>
         </is>
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE DINARD</t>
         </is>
       </c>
       <c r="E96" s="15" t="inlineStr">
         <is>
-          <t>Crédit d'heures</t>
+          <t xml:space="preserve">Ajout module caisse parking / Ajout export finance pour module placier </t>
         </is>
       </c>
       <c r="F96" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G96" s="15" t="inlineStr">
@@ -7607,64 +7607,64 @@
       </c>
       <c r="I96" s="15" t="inlineStr">
         <is>
-          <t>13/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J96" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K96" s="15" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L96" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31273</t>
+          <t>PDMDEP-31346</t>
         </is>
       </c>
       <c r="M96" s="15" t="inlineStr">
         <is>
-          <t>0000ENATTENTEVRAIBDC</t>
+          <t>00157037</t>
         </is>
       </c>
       <c r="N96" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O96" s="16" t="n">
-        <v>28.1</v>
+        <v>0</v>
       </c>
       <c r="P96" s="16" t="n">
-        <v>18.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31269</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[DIJON METROPOLE] - Crédit d'heures</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Crédit d'heures</t>
         </is>
       </c>
       <c r="F97" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G97" s="12" t="inlineStr">
@@ -7674,49 +7674,49 @@
       </c>
       <c r="H97" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>13/02/2026</t>
         </is>
       </c>
       <c r="J97" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K97" s="12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L97" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31273</t>
         </is>
       </c>
       <c r="M97" s="12" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>0000ENATTENTEVRAIBDC</t>
         </is>
       </c>
       <c r="N97" s="13" t="n">
-        <v>130</v>
-      </c>
-      <c r="O97" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O97" s="13" t="n">
+        <v>28.1</v>
       </c>
       <c r="P97" s="13" t="n">
-        <v>0</v>
+        <v>18.73</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
@@ -7726,12 +7726,12 @@
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E98" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F98" s="15" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="I98" s="15" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J98" s="15" t="n">
@@ -7762,16 +7762,16 @@
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M98" s="15" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N98" s="16" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O98" s="17" t="n">
         <v>0</v>
@@ -7783,12 +7783,12 @@
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30358</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARGELES-SUR-MER</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
@@ -7823,27 +7823,27 @@
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J99" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K99" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L99" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30366</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M99" s="12" t="inlineStr">
         <is>
-          <t>00154569</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N99" s="13" t="n">
-        <v>1000</v>
+        <v>255</v>
       </c>
       <c r="O99" s="17" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-30358</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE D'ARGELES-SUR-MER</t>
         </is>
       </c>
       <c r="E100" s="15" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F100" s="15" t="inlineStr">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="J100" s="15" t="n">
@@ -7906,16 +7906,16 @@
       </c>
       <c r="L100" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-30366</t>
         </is>
       </c>
       <c r="M100" s="15" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00154569</t>
         </is>
       </c>
       <c r="N100" s="16" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="O100" s="17" t="n">
         <v>0</v>
@@ -7927,27 +7927,27 @@
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30311</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAEN</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>GeODP - Modification des marges via activation Editique</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F101" s="12" t="inlineStr">
@@ -7967,7 +7967,7 @@
       </c>
       <c r="I101" s="12" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J101" s="12" t="n">
@@ -7978,16 +7978,16 @@
       </c>
       <c r="L101" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30316</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M101" s="12" t="inlineStr">
         <is>
-          <t>00154362</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N101" s="13" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="O101" s="17" t="n">
         <v>0</v>
@@ -7999,32 +7999,32 @@
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30311</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D102" s="15" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE CAEN</t>
         </is>
       </c>
       <c r="E102" s="15" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="F102" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G102" s="15" t="inlineStr">
@@ -8034,34 +8034,34 @@
       </c>
       <c r="H102" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I102" s="15" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="J102" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K102" s="15" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30316</t>
         </is>
       </c>
       <c r="M102" s="15" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154362</t>
         </is>
       </c>
       <c r="N102" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" s="16" t="n">
+        <v>200</v>
+      </c>
+      <c r="O102" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P102" s="16" t="n">
@@ -8071,12 +8071,12 @@
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30062</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>Commune de Saint-Dizier</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J103" s="12" t="n">
@@ -8122,18 +8122,18 @@
       </c>
       <c r="L103" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30063</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M103" s="12" t="inlineStr">
         <is>
-          <t>00153633</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N103" s="13" t="n">
-        <v>350</v>
-      </c>
-      <c r="O103" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P103" s="13" t="n">
@@ -8143,27 +8143,27 @@
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-30062</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>Commune de Saint-Dizier</t>
         </is>
       </c>
       <c r="E104" s="15" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="F104" s="15" t="inlineStr">
@@ -8183,29 +8183,29 @@
       </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J104" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K104" s="15" t="n">
-        <v>6.25</v>
+        <v>0.75</v>
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-30063</t>
         </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00153633</t>
         </is>
       </c>
       <c r="N104" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" s="16" t="n">
+        <v>350</v>
+      </c>
+      <c r="O104" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P104" s="16" t="n">
@@ -8215,32 +8215,32 @@
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29685</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE FREJUS - Migration V2 ODP</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE FREJUS</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Migration V2 ODP</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F105" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G105" s="12" t="inlineStr">
@@ -8250,28 +8250,28 @@
       </c>
       <c r="H105" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>12/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J105" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>0.5</v>
+        <v>6.25</v>
       </c>
       <c r="L105" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29690</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M105" s="12" t="inlineStr">
         <is>
-          <t>00152489</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N105" s="13" t="n">
@@ -8287,32 +8287,32 @@
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-29685</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>COMMUNE DE FREJUS - Migration V2 ODP</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE FREJUS</t>
         </is>
       </c>
       <c r="E106" s="15" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Migration V2 ODP</t>
         </is>
       </c>
       <c r="F106" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G106" s="15" t="inlineStr">
@@ -8322,28 +8322,28 @@
       </c>
       <c r="H106" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I106" s="15" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="J106" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K106" s="15" t="n">
-        <v>0.83</v>
+        <v>0.5</v>
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-29690</t>
         </is>
       </c>
       <c r="M106" s="15" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00152489</t>
         </is>
       </c>
       <c r="N106" s="16" t="n">
@@ -8410,12 +8410,12 @@
       </c>
       <c r="L107" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M107" s="12" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N107" s="13" t="n">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N108" s="16" t="n">
@@ -8503,32 +8503,32 @@
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29208</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>Commune de Calais - GEODP2 new</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>Commune de Calais</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F109" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G109" s="12" t="inlineStr">
@@ -8538,28 +8538,28 @@
       </c>
       <c r="H109" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>22/12/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J109" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K109" s="12" t="n">
-        <v>4.5</v>
+        <v>0.83</v>
       </c>
       <c r="L109" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29211</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M109" s="12" t="inlineStr">
         <is>
-          <t>00148286</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N109" s="13" t="n">
@@ -8575,30 +8575,32 @@
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29122</t>
+          <t>PDMDEP-29208</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES DEUX SEVRES (CD 79) - LITTERALIS - Flux WFS communication</t>
+          <t>Commune de Calais - GEODP2 new</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
-        </is>
-      </c>
-      <c r="E110" s="15" t="n">
-        <v/>
+          <t>Commune de Calais</t>
+        </is>
+      </c>
+      <c r="E110" s="15" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
       </c>
       <c r="F110" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G110" s="15" t="inlineStr">
@@ -8608,34 +8610,34 @@
       </c>
       <c r="H110" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
-          <t>19/12/2025</t>
+          <t>22/12/2025</t>
         </is>
       </c>
       <c r="J110" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K110" s="15" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29124</t>
+          <t>PDMDEP-29211</t>
         </is>
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
-          <t>00148148</t>
+          <t>00148286</t>
         </is>
       </c>
       <c r="N110" s="16" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="O110" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="16" t="n">
@@ -8645,32 +8647,30 @@
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29122</t>
         </is>
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t>DEPARTEMENT DES DEUX SEVRES (CD 79) - LITTERALIS - Flux WFS communication</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
-        </is>
-      </c>
-      <c r="E111" s="12" t="inlineStr">
-        <is>
-          <t>Migration V2</t>
-        </is>
+          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="n">
+        <v/>
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G111" s="12" t="inlineStr">
@@ -8680,34 +8680,34 @@
       </c>
       <c r="H111" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>19/12/2025</t>
         </is>
       </c>
       <c r="J111" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L111" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28531</t>
+          <t>PDMDEP-29124</t>
         </is>
       </c>
       <c r="M111" s="12" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00148148</t>
         </is>
       </c>
       <c r="N111" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O111" s="13" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="O111" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P111" s="13" t="n">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-28531</t>
         </is>
       </c>
       <c r="M112" s="15" t="inlineStr">
@@ -8780,39 +8780,41 @@
         <v>0</v>
       </c>
       <c r="O112" s="16" t="n">
-        <v>405</v>
+        <v>0</v>
       </c>
       <c r="P112" s="16" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E113" s="12" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G113" s="12" t="inlineStr">
@@ -8822,49 +8824,49 @@
       </c>
       <c r="H113" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J113" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L113" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M113" s="12" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N113" s="13" t="n">
-        <v>2812.32</v>
-      </c>
-      <c r="O113" s="17" t="n">
-        <v>300.28</v>
+        <v>0</v>
+      </c>
+      <c r="O113" s="13" t="n">
+        <v>405</v>
       </c>
       <c r="P113" s="13" t="n">
-        <v>200.19</v>
+        <v>810</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
@@ -8874,13 +8876,11 @@
       </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E114" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E114" s="15" t="n">
+        <v/>
       </c>
       <c r="F114" s="15" t="inlineStr">
         <is>
@@ -8899,33 +8899,33 @@
       </c>
       <c r="I114" s="15" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J114" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K114" s="15" t="n">
-        <v>1.15</v>
+        <v>3</v>
       </c>
       <c r="L114" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M114" s="15" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N114" s="16" t="n">
-        <v>392.5</v>
+        <v>2812.32</v>
       </c>
       <c r="O114" s="17" t="n">
-        <v>0</v>
+        <v>300.28</v>
       </c>
       <c r="P114" s="16" t="n">
-        <v>0</v>
+        <v>100.09</v>
       </c>
     </row>
     <row r="115">
@@ -8982,16 +8982,16 @@
       </c>
       <c r="L115" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M115" s="12" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N115" s="13" t="n">
-        <v>1556.25</v>
+        <v>392.5</v>
       </c>
       <c r="O115" s="17" t="n">
         <v>0</v>
@@ -9054,16 +9054,16 @@
       </c>
       <c r="L116" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M116" s="15" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N116" s="16" t="n">
-        <v>1790</v>
+        <v>1556.25</v>
       </c>
       <c r="O116" s="17" t="n">
         <v>0</v>
@@ -9126,18 +9126,18 @@
       </c>
       <c r="L117" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M117" s="12" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N117" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O117" s="13" t="n">
+        <v>1790</v>
+      </c>
+      <c r="O117" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P117" s="13" t="n">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L118" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M118" s="15" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N118" s="16" t="n">
@@ -9219,12 +9219,12 @@
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
@@ -9234,11 +9234,13 @@
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E119" s="12" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E119" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F119" s="12" t="inlineStr">
         <is>
@@ -9252,28 +9254,28 @@
       </c>
       <c r="H119" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I119" s="12" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J119" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K119" s="12" t="n">
-        <v>4.25</v>
+        <v>1.15</v>
       </c>
       <c r="L119" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M119" s="12" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N119" s="13" t="n">
@@ -9289,12 +9291,12 @@
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C120" s="15" t="inlineStr">
@@ -9304,7 +9306,7 @@
       </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
         </is>
       </c>
       <c r="E120" s="15" t="n">
@@ -9322,34 +9324,34 @@
       </c>
       <c r="H120" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J120" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K120" s="15" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="L120" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M120" s="15" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N120" s="16" t="n">
-        <v>732</v>
-      </c>
-      <c r="O120" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P120" s="16" t="n">
@@ -9359,12 +9361,12 @@
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
@@ -9374,38 +9376,52 @@
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>CD74</t>
-        </is>
-      </c>
-      <c r="E121" s="12" t="inlineStr">
-        <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F121" s="12" t="inlineStr"/>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="n">
+        <v/>
+      </c>
+      <c r="F121" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H121" s="12" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H121" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I121" s="12" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J121" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L121" s="12" t="inlineStr"/>
-      <c r="M121" s="12" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L121" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27557</t>
+        </is>
+      </c>
+      <c r="M121" s="12" t="inlineStr">
+        <is>
+          <t>00144532</t>
+        </is>
+      </c>
       <c r="N121" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O121" s="13" t="n">
+        <v>732</v>
+      </c>
+      <c r="O121" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P121" s="13" t="n">
@@ -9415,12 +9431,12 @@
     <row r="122">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C122" s="15" t="inlineStr">
@@ -9430,83 +9446,67 @@
       </c>
       <c r="D122" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
-        </is>
-      </c>
-      <c r="E122" s="15" t="n">
-        <v/>
-      </c>
-      <c r="F122" s="15" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E122" s="15" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F122" s="15" t="inlineStr"/>
       <c r="G122" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H122" s="15" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H122" s="15" t="inlineStr"/>
       <c r="I122" s="15" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J122" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K122" s="15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L122" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-26814</t>
-        </is>
-      </c>
-      <c r="M122" s="15" t="inlineStr">
-        <is>
-          <t>00142941</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L122" s="15" t="inlineStr"/>
+      <c r="M122" s="15" t="inlineStr"/>
       <c r="N122" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O122" s="16" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="P122" s="16" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
-        </is>
-      </c>
-      <c r="E123" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement LiEx</t>
-        </is>
+          <t>VILLE DE VILLEJUIF</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="n">
+        <v/>
       </c>
       <c r="F123" s="12" t="inlineStr">
         <is>
@@ -9520,63 +9520,65 @@
       </c>
       <c r="H123" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I123" s="12" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J123" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K123" s="12" t="n">
-        <v>9.25</v>
+        <v>1.25</v>
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-26783</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
         <is>
-          <t>00142659</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N123" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O123" s="13" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="P123" s="13" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C124" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
-        </is>
-      </c>
-      <c r="E124" s="15" t="n">
-        <v/>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E124" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
       </c>
       <c r="F124" s="15" t="inlineStr">
         <is>
@@ -9595,29 +9597,29 @@
       </c>
       <c r="I124" s="15" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J124" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K124" s="15" t="n">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="L124" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M124" s="15" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N124" s="16" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O124" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P124" s="16" t="n">
@@ -9627,12 +9629,12 @@
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24765</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>[COLOMBES] -  Litteralis - Interface Pastell</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
@@ -9642,7 +9644,7 @@
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE COLOMBES - DSIO</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E125" s="12" t="n">
@@ -9660,34 +9662,34 @@
       </c>
       <c r="H125" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I125" s="12" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J125" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K125" s="12" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="L125" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28062</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M125" s="12" t="inlineStr">
         <is>
-          <t>500768</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N125" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O125" s="13" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O125" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P125" s="13" t="n">
@@ -9697,22 +9699,22 @@
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-24765</t>
         </is>
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>[COLOMBES] -  Litteralis - Interface Pastell</t>
         </is>
       </c>
       <c r="C126" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>VILLE DE COLOMBES - DSIO</t>
         </is>
       </c>
       <c r="E126" s="15" t="n">
@@ -9735,23 +9737,23 @@
       </c>
       <c r="I126" s="15" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="J126" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="L126" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-28062</t>
         </is>
       </c>
       <c r="M126" s="15" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>500768</t>
         </is>
       </c>
       <c r="N126" s="16" t="n">
@@ -9767,12 +9769,12 @@
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
@@ -9782,7 +9784,7 @@
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E127" s="12" t="n">
@@ -9800,28 +9802,28 @@
       </c>
       <c r="H127" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I127" s="12" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J127" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K127" s="12" t="n">
-        <v>2.88</v>
+        <v>0.5</v>
       </c>
       <c r="L127" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27996</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M127" s="12" t="inlineStr">
         <is>
-          <t>501219</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N127" s="13" t="n">
@@ -9882,16 +9884,16 @@
         <v>10</v>
       </c>
       <c r="K128" s="15" t="n">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="L128" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M128" s="15" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N128" s="16" t="n">
@@ -9907,22 +9909,22 @@
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E129" s="12" t="n">
@@ -9945,29 +9947,29 @@
       </c>
       <c r="I129" s="12" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J129" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K129" s="12" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="L129" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M129" s="12" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N129" s="13" t="n">
-        <v>2323</v>
-      </c>
-      <c r="O129" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P129" s="13" t="n">
@@ -9977,22 +9979,22 @@
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23486</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- AJOUT BALISE FILIEN</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C130" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E130" s="15" t="n">
@@ -10000,7 +10002,7 @@
       </c>
       <c r="F130" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G130" s="15" t="inlineStr">
@@ -10010,32 +10012,32 @@
       </c>
       <c r="H130" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I130" s="15" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J130" s="15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K130" s="15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="L130" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27493</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M130" s="15" t="inlineStr">
         <is>
-          <t>495699</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N130" s="16" t="n">
-        <v>964.1</v>
+        <v>2323</v>
       </c>
       <c r="O130" s="17" t="n">
         <v>0</v>
@@ -10047,12 +10049,12 @@
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23484</t>
+          <t>PDMDEP-23486</t>
         </is>
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
+          <t>METROPOLE TOULON- AJOUT BALISE FILIEN</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
@@ -10096,19 +10098,19 @@
       </c>
       <c r="L131" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27494</t>
+          <t>PDMDEP-27493</t>
         </is>
       </c>
       <c r="M131" s="12" t="inlineStr">
         <is>
-          <t>495695</t>
+          <t>495699</t>
         </is>
       </c>
       <c r="N131" s="13" t="n">
-        <v>140.4</v>
+        <v>964.1</v>
       </c>
       <c r="O131" s="17" t="n">
-        <v>70.2</v>
+        <v>0</v>
       </c>
       <c r="P131" s="13" t="n">
         <v>0</v>
@@ -10117,22 +10119,22 @@
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23484</t>
         </is>
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
         </is>
       </c>
       <c r="C132" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E132" s="15" t="n">
@@ -10140,7 +10142,7 @@
       </c>
       <c r="F132" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G132" s="15" t="inlineStr">
@@ -10150,35 +10152,35 @@
       </c>
       <c r="H132" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I132" s="15" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="J132" s="15" t="n">
         <v>12</v>
       </c>
       <c r="K132" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L132" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-27494</t>
         </is>
       </c>
       <c r="M132" s="15" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>495695</t>
         </is>
       </c>
       <c r="N132" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O132" s="16" t="n">
-        <v>0</v>
+        <v>140.4</v>
+      </c>
+      <c r="O132" s="17" t="n">
+        <v>70.2</v>
       </c>
       <c r="P132" s="16" t="n">
         <v>0</v>
@@ -10187,22 +10189,22 @@
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22996</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E133" s="12" t="n">
@@ -10220,28 +10222,28 @@
       </c>
       <c r="H133" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I133" s="12" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J133" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L133" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28051</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M133" s="12" t="inlineStr">
         <is>
-          <t>487190</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N133" s="13" t="n">
@@ -10257,22 +10259,22 @@
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-22996</t>
         </is>
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
         </is>
       </c>
       <c r="C134" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D134" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E134" s="15" t="n">
@@ -10290,28 +10292,28 @@
       </c>
       <c r="H134" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I134" s="15" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="J134" s="15" t="n">
         <v>12</v>
       </c>
       <c r="K134" s="15" t="n">
-        <v>0.19</v>
+        <v>2</v>
       </c>
       <c r="L134" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-28051</t>
         </is>
       </c>
       <c r="M134" s="15" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>487190</t>
         </is>
       </c>
       <c r="N134" s="16" t="n">
@@ -10376,12 +10378,12 @@
       </c>
       <c r="L135" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M135" s="12" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N135" s="13" t="n">
@@ -10412,7 +10414,7 @@
       </c>
       <c r="D136" s="15" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E136" s="15" t="n">
@@ -10446,12 +10448,12 @@
       </c>
       <c r="L136" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M136" s="15" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N136" s="16" t="n">
@@ -10482,7 +10484,7 @@
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E137" s="12" t="n">
@@ -10516,12 +10518,12 @@
       </c>
       <c r="L137" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M137" s="12" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N137" s="13" t="n">
@@ -10537,12 +10539,12 @@
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22496</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - LITTERALIS Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C138" s="15" t="inlineStr">
@@ -10552,7 +10554,7 @@
       </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E138" s="15" t="n">
@@ -10570,28 +10572,28 @@
       </c>
       <c r="H138" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
-          <t>23/06/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J138" s="15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K138" s="15" t="n">
-        <v>0.5</v>
+        <v>0.19</v>
       </c>
       <c r="L138" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27371</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M138" s="15" t="inlineStr">
         <is>
-          <t>481817</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N138" s="16" t="n">
@@ -10607,22 +10609,22 @@
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22496</t>
         </is>
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[VILLEJUIF] - LITTERALIS Pastell</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E139" s="12" t="n">
@@ -10645,23 +10647,23 @@
       </c>
       <c r="I139" s="12" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>23/06/2025</t>
         </is>
       </c>
       <c r="J139" s="12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K139" s="12" t="n">
         <v>0.5</v>
       </c>
       <c r="L139" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27371</t>
         </is>
       </c>
       <c r="M139" s="12" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>481817</t>
         </is>
       </c>
       <c r="N139" s="13" t="n">
@@ -10677,22 +10679,22 @@
     <row r="140">
       <c r="A140" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21546</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C140" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D140" s="15" t="inlineStr">
         <is>
-          <t>VILLEURBANNE</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E140" s="15" t="n">
@@ -10700,7 +10702,7 @@
       </c>
       <c r="F140" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G140" s="15" t="inlineStr">
@@ -10715,29 +10717,29 @@
       </c>
       <c r="I140" s="15" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J140" s="15" t="n">
         <v>14</v>
       </c>
       <c r="K140" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L140" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28038</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M140" s="15" t="inlineStr">
         <is>
-          <t>478867</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N140" s="16" t="n">
-        <v>482.72</v>
-      </c>
-      <c r="O140" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P140" s="16" t="n">
@@ -10747,18 +10749,22 @@
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21544</t>
+          <t>PDMDEP-21546</t>
         </is>
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>[La Ciotat] Accompagnement modélisation Littéralis Expert</t>
-        </is>
-      </c>
-      <c r="C141" s="12" t="inlineStr"/>
+          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
+        </is>
+      </c>
+      <c r="C141" s="12" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>LA CIOTAT</t>
+          <t>VILLEURBANNE</t>
         </is>
       </c>
       <c r="E141" s="12" t="n">
@@ -10766,7 +10772,7 @@
       </c>
       <c r="F141" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G141" s="12" t="inlineStr">
@@ -10792,19 +10798,19 @@
       </c>
       <c r="L141" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28037</t>
+          <t>PDMDEP-28038</t>
         </is>
       </c>
       <c r="M141" s="12" t="inlineStr">
         <is>
-          <t>474055</t>
+          <t>478867</t>
         </is>
       </c>
       <c r="N141" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O141" s="13" t="n">
-        <v>575</v>
+        <v>482.72</v>
+      </c>
+      <c r="O141" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P141" s="13" t="n">
         <v>0</v>
@@ -10813,22 +10819,18 @@
     <row r="142">
       <c r="A142" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21544</t>
         </is>
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
-        </is>
-      </c>
-      <c r="C142" s="15" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
+          <t>[La Ciotat] Accompagnement modélisation Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C142" s="15" t="inlineStr"/>
       <c r="D142" s="15" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>LA CIOTAT</t>
         </is>
       </c>
       <c r="E142" s="15" t="n">
@@ -10846,35 +10848,35 @@
       </c>
       <c r="H142" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I142" s="15" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="J142" s="15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K142" s="15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L142" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-28037</t>
         </is>
       </c>
       <c r="M142" s="15" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>474055</t>
         </is>
       </c>
       <c r="N142" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O142" s="16" t="n">
-        <v>0</v>
+        <v>575</v>
       </c>
       <c r="P142" s="16" t="n">
         <v>0</v>
@@ -10883,22 +10885,22 @@
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E143" s="12" t="n">
@@ -10916,34 +10918,34 @@
       </c>
       <c r="H143" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I143" s="12" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J143" s="12" t="n">
         <v>15</v>
       </c>
       <c r="K143" s="12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="L143" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M143" s="12" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N143" s="13" t="n">
-        <v>250</v>
-      </c>
-      <c r="O143" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P143" s="13" t="n">
@@ -10953,22 +10955,22 @@
     <row r="144">
       <c r="A144" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C144" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D144" s="15" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E144" s="15" t="n">
@@ -10991,27 +10993,27 @@
       </c>
       <c r="I144" s="15" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J144" s="15" t="n">
         <v>15</v>
       </c>
       <c r="K144" s="15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L144" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M144" s="15" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N144" s="16" t="n">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="O144" s="17" t="n">
         <v>0</v>
@@ -11023,22 +11025,22 @@
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E145" s="12" t="n">
@@ -11054,24 +11056,36 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H145" s="12" t="inlineStr"/>
+      <c r="H145" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I145" s="12" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J145" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K145" s="12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L145" s="12" t="inlineStr"/>
-      <c r="M145" s="12" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L145" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M145" s="12" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N145" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O145" s="13" t="n">
+        <v>230</v>
+      </c>
+      <c r="O145" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P145" s="13" t="n">
@@ -11081,22 +11095,22 @@
     <row r="146">
       <c r="A146" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C146" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E146" s="15" t="n">
@@ -11112,14 +11126,10 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H146" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H146" s="15" t="inlineStr"/>
       <c r="I146" s="15" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J146" s="15" t="n">
@@ -11128,16 +11138,8 @@
       <c r="K146" s="15" t="n">
         <v>1.25</v>
       </c>
-      <c r="L146" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28027</t>
-        </is>
-      </c>
-      <c r="M146" s="15" t="inlineStr">
-        <is>
-          <t>470688</t>
-        </is>
-      </c>
+      <c r="L146" s="15" t="inlineStr"/>
+      <c r="M146" s="15" t="inlineStr"/>
       <c r="N146" s="16" t="n">
         <v>0</v>
       </c>
@@ -11151,12 +11153,12 @@
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
@@ -11166,7 +11168,7 @@
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E147" s="12" t="n">
@@ -11184,28 +11186,28 @@
       </c>
       <c r="H147" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I147" s="12" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J147" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K147" s="12" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="L147" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M147" s="12" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N147" s="13" t="n">
@@ -11221,12 +11223,12 @@
     <row r="148">
       <c r="A148" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C148" s="15" t="inlineStr">
@@ -11236,7 +11238,7 @@
       </c>
       <c r="D148" s="15" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E148" s="15" t="n">
@@ -11254,28 +11256,28 @@
       </c>
       <c r="H148" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I148" s="15" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J148" s="15" t="n">
         <v>16</v>
       </c>
       <c r="K148" s="15" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L148" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M148" s="15" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N148" s="16" t="n">
@@ -11291,12 +11293,12 @@
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19385</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
@@ -11306,7 +11308,7 @@
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARCUEIL</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E149" s="12" t="n">
@@ -11329,23 +11331,23 @@
       </c>
       <c r="I149" s="12" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J149" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K149" s="12" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L149" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27535</t>
+          <t>PDMDEP-27377</t>
         </is>
       </c>
       <c r="M149" s="12" t="inlineStr">
         <is>
-          <t>465345</t>
+          <t>478048</t>
         </is>
       </c>
       <c r="N149" s="13" t="n">
@@ -11361,22 +11363,22 @@
     <row r="150">
       <c r="A150" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-19385</t>
         </is>
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
         </is>
       </c>
       <c r="C150" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>COMMUNE D'ARCUEIL</t>
         </is>
       </c>
       <c r="E150" s="15" t="n">
@@ -11389,27 +11391,35 @@
       </c>
       <c r="G150" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H150" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I150" s="15" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="J150" s="15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K150" s="15" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L150" s="15" t="inlineStr"/>
-      <c r="M150" s="15" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L150" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27535</t>
+        </is>
+      </c>
+      <c r="M150" s="15" t="inlineStr">
+        <is>
+          <t>465345</t>
+        </is>
+      </c>
       <c r="N150" s="16" t="n">
         <v>0</v>
       </c>
@@ -11423,22 +11433,22 @@
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E151" s="12" t="n">
@@ -11456,7 +11466,7 @@
       </c>
       <c r="H151" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I151" s="12" t="inlineStr">
@@ -11468,7 +11478,7 @@
         <v>19</v>
       </c>
       <c r="K151" s="12" t="n">
-        <v>5</v>
+        <v>0.75</v>
       </c>
       <c r="L151" s="12" t="inlineStr"/>
       <c r="M151" s="12" t="inlineStr"/>
@@ -11485,22 +11495,22 @@
     <row r="152">
       <c r="A152" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18212</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>[Besancon] Acquisition</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C152" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D152" s="15" t="inlineStr">
         <is>
-          <t>Besançon</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E152" s="15" t="n">
@@ -11508,7 +11518,7 @@
       </c>
       <c r="F152" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G152" s="15" t="inlineStr">
@@ -11530,7 +11540,7 @@
         <v>19</v>
       </c>
       <c r="K152" s="15" t="n">
-        <v>1.5</v>
+        <v>5.25</v>
       </c>
       <c r="L152" s="15" t="inlineStr"/>
       <c r="M152" s="15" t="inlineStr"/>
@@ -11547,12 +11557,12 @@
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18212</t>
         </is>
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[Besancon] Acquisition</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
@@ -11562,7 +11572,7 @@
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Besançon</t>
         </is>
       </c>
       <c r="E153" s="12" t="n">
@@ -11575,39 +11585,31 @@
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H153" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I153" s="12" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J153" s="12" t="n">
         <v>19</v>
       </c>
       <c r="K153" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L153" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M153" s="12" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L153" s="12" t="inlineStr"/>
+      <c r="M153" s="12" t="inlineStr"/>
       <c r="N153" s="13" t="n">
-        <v>240</v>
-      </c>
-      <c r="O153" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P153" s="13" t="n">
@@ -11617,22 +11619,22 @@
     <row r="154">
       <c r="A154" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C154" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D154" s="15" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E154" s="15" t="n">
@@ -11640,7 +11642,7 @@
       </c>
       <c r="F154" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G154" s="15" t="inlineStr">
@@ -11650,34 +11652,34 @@
       </c>
       <c r="H154" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I154" s="15" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J154" s="15" t="n">
         <v>19</v>
       </c>
       <c r="K154" s="15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L154" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34362</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M154" s="15" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N154" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O154" s="16" t="n">
+        <v>240</v>
+      </c>
+      <c r="O154" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P154" s="16" t="n">
@@ -11702,7 +11704,7 @@
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E155" s="12" t="n">
@@ -11732,11 +11734,11 @@
         <v>19</v>
       </c>
       <c r="K155" s="12" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="L155" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-34362</t>
         </is>
       </c>
       <c r="M155" s="12" t="inlineStr">
@@ -11757,22 +11759,22 @@
     <row r="156">
       <c r="A156" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-16868</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>[Limoges] migration placier</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C156" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D156" s="15" t="inlineStr">
         <is>
-          <t>Limoges</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E156" s="15" t="n">
@@ -11780,32 +11782,40 @@
       </c>
       <c r="F156" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G156" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H156" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I156" s="15" t="inlineStr">
         <is>
-          <t>26/09/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J156" s="15" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K156" s="15" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="L156" s="15" t="inlineStr"/>
-      <c r="M156" s="15" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L156" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28020</t>
+        </is>
+      </c>
+      <c r="M156" s="15" t="inlineStr">
+        <is>
+          <t>458057</t>
+        </is>
+      </c>
       <c r="N156" s="16" t="n">
         <v>0</v>
       </c>
@@ -11819,22 +11829,22 @@
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-16868</t>
         </is>
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[Limoges] migration placier</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>Limoges</t>
         </is>
       </c>
       <c r="E157" s="12" t="n">
@@ -11842,7 +11852,7 @@
       </c>
       <c r="F157" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G157" s="12" t="inlineStr">
@@ -11852,19 +11862,19 @@
       </c>
       <c r="H157" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I157" s="12" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>26/09/2024</t>
         </is>
       </c>
       <c r="J157" s="12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K157" s="12" t="n">
-        <v>0.25</v>
+        <v>4.75</v>
       </c>
       <c r="L157" s="12" t="inlineStr"/>
       <c r="M157" s="12" t="inlineStr"/>
@@ -11881,22 +11891,22 @@
     <row r="158">
       <c r="A158" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C158" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D158" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E158" s="15" t="n">
@@ -11909,7 +11919,7 @@
       </c>
       <c r="G158" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H158" s="15" t="inlineStr">
@@ -11919,25 +11929,17 @@
       </c>
       <c r="I158" s="15" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J158" s="15" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K158" s="15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L158" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28003</t>
-        </is>
-      </c>
-      <c r="M158" s="15" t="inlineStr">
-        <is>
-          <t>412981</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L158" s="15" t="inlineStr"/>
+      <c r="M158" s="15" t="inlineStr"/>
       <c r="N158" s="16" t="n">
         <v>0</v>
       </c>
@@ -11951,12 +11953,12 @@
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14551</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B159" s="12" t="inlineStr">
         <is>
-          <t>[Perpignan] Interface formulaire</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
@@ -11966,7 +11968,7 @@
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>[Perpignan]</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E159" s="12" t="n">
@@ -11979,7 +11981,7 @@
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H159" s="12" t="inlineStr">
@@ -11989,17 +11991,25 @@
       </c>
       <c r="I159" s="12" t="inlineStr">
         <is>
-          <t>14/03/2024</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J159" s="12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K159" s="12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L159" s="12" t="inlineStr"/>
-      <c r="M159" s="12" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L159" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28003</t>
+        </is>
+      </c>
+      <c r="M159" s="12" t="inlineStr">
+        <is>
+          <t>412981</t>
+        </is>
+      </c>
       <c r="N159" s="13" t="n">
         <v>0</v>
       </c>
@@ -12013,22 +12023,22 @@
     <row r="160">
       <c r="A160" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14273</t>
+          <t>PDMDEP-14551</t>
         </is>
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>[CD51 - MARNE] Modélisation, visa et Interface BG</t>
+          <t>[Perpignan] Interface formulaire</t>
         </is>
       </c>
       <c r="C160" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D160" s="15" t="inlineStr">
         <is>
-          <t>CD Marne</t>
+          <t>[Perpignan]</t>
         </is>
       </c>
       <c r="E160" s="15" t="n">
@@ -12051,14 +12061,14 @@
       </c>
       <c r="I160" s="15" t="inlineStr">
         <is>
-          <t>20/02/2024</t>
+          <t>14/03/2024</t>
         </is>
       </c>
       <c r="J160" s="15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K160" s="15" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="L160" s="15" t="inlineStr"/>
       <c r="M160" s="15" t="inlineStr"/>
@@ -12075,22 +12085,22 @@
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14254</t>
+          <t>PDMDEP-14273</t>
         </is>
       </c>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
+          <t>[CD51 - MARNE] Modélisation, visa et Interface BG</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>Dijon métropole</t>
+          <t>CD Marne</t>
         </is>
       </c>
       <c r="E161" s="12" t="n">
@@ -12113,14 +12123,14 @@
       </c>
       <c r="I161" s="12" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>20/02/2024</t>
         </is>
       </c>
       <c r="J161" s="12" t="n">
         <v>29</v>
       </c>
       <c r="K161" s="12" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L161" s="12" t="inlineStr"/>
       <c r="M161" s="12" t="inlineStr"/>
@@ -12137,22 +12147,22 @@
     <row r="162">
       <c r="A162" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14095</t>
+          <t>PDMDEP-14254</t>
         </is>
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
         </is>
       </c>
       <c r="C162" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D162" s="15" t="inlineStr">
         <is>
-          <t>CC du Pays Sabolien</t>
+          <t>Dijon métropole</t>
         </is>
       </c>
       <c r="E162" s="15" t="n">
@@ -12170,19 +12180,19 @@
       </c>
       <c r="H162" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I162" s="15" t="inlineStr">
         <is>
-          <t>31/01/2024</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="J162" s="15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K162" s="15" t="n">
-        <v>7.25</v>
+        <v>1</v>
       </c>
       <c r="L162" s="15" t="inlineStr"/>
       <c r="M162" s="15" t="inlineStr"/>
@@ -12199,22 +12209,22 @@
     <row r="163">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-14095</t>
         </is>
       </c>
       <c r="B163" s="12" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>CC du Pays Sabolien</t>
         </is>
       </c>
       <c r="E163" s="12" t="n">
@@ -12227,35 +12237,27 @@
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H163" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I163" s="12" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>31/01/2024</t>
         </is>
       </c>
       <c r="J163" s="12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K163" s="12" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="L163" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M163" s="12" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>7.25</v>
+      </c>
+      <c r="L163" s="12" t="inlineStr"/>
+      <c r="M163" s="12" t="inlineStr"/>
       <c r="N163" s="13" t="n">
         <v>0</v>
       </c>
@@ -12269,22 +12271,22 @@
     <row r="164">
       <c r="A164" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C164" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D164" s="15" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E164" s="15" t="n">
@@ -12297,20 +12299,24 @@
       </c>
       <c r="G164" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H164" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H164" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I164" s="15" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J164" s="15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K164" s="15" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L164" s="15" t="inlineStr"/>
       <c r="M164" s="15" t="inlineStr"/>
@@ -12327,22 +12333,22 @@
     <row r="165">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B165" s="12" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E165" s="12" t="n">
@@ -12355,31 +12361,35 @@
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H165" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I165" s="12" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J165" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K165" s="12" t="n">
-        <v>1.75</v>
+        <v>9.25</v>
       </c>
       <c r="L165" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M165" s="12" t="inlineStr"/>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M165" s="12" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N165" s="13" t="n">
         <v>0</v>
       </c>
@@ -12393,12 +12403,12 @@
     <row r="166">
       <c r="A166" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C166" s="15" t="inlineStr">
@@ -12408,7 +12418,7 @@
       </c>
       <c r="D166" s="15" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E166" s="15" t="n">
@@ -12421,24 +12431,20 @@
       </c>
       <c r="G166" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H166" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H166" s="15" t="inlineStr"/>
       <c r="I166" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J166" s="15" t="n">
         <v>34</v>
       </c>
       <c r="K166" s="15" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L166" s="15" t="inlineStr"/>
       <c r="M166" s="15" t="inlineStr"/>
@@ -12455,28 +12461,26 @@
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12241</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B167" s="12" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe]</t>
-        </is>
-      </c>
-      <c r="E167" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement de Littéralis Expert</t>
-        </is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E167" s="12" t="n">
+        <v/>
       </c>
       <c r="F167" s="12" t="inlineStr">
         <is>
@@ -12495,16 +12499,20 @@
       </c>
       <c r="I167" s="12" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J167" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K167" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L167" s="12" t="inlineStr"/>
+        <v>1.75</v>
+      </c>
+      <c r="L167" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
       <c r="M167" s="12" t="inlineStr"/>
       <c r="N167" s="13" t="n">
         <v>0</v>
@@ -12519,28 +12527,26 @@
     <row r="168">
       <c r="A168" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C168" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D168" s="15" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E168" s="15" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E168" s="15" t="n">
+        <v/>
       </c>
       <c r="F168" s="15" t="inlineStr">
         <is>
@@ -12554,7 +12560,7 @@
       </c>
       <c r="H168" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I168" s="15" t="inlineStr">
@@ -12566,7 +12572,7 @@
         <v>34</v>
       </c>
       <c r="K168" s="15" t="n">
-        <v>8.75</v>
+        <v>1</v>
       </c>
       <c r="L168" s="15" t="inlineStr"/>
       <c r="M168" s="15" t="inlineStr"/>
@@ -12583,23 +12589,27 @@
     <row r="169">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12241</t>
         </is>
       </c>
       <c r="B169" s="12" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C169" s="12" t="inlineStr"/>
+          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C169" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>[SM Routes de Guadeloupe]</t>
         </is>
       </c>
       <c r="E169" s="12" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Déploiement de Littéralis Expert</t>
         </is>
       </c>
       <c r="F169" s="12" t="inlineStr">
@@ -12619,14 +12629,14 @@
       </c>
       <c r="I169" s="12" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J169" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K169" s="12" t="n">
-        <v>1.75</v>
+        <v>0.5</v>
       </c>
       <c r="L169" s="12" t="inlineStr"/>
       <c r="M169" s="12" t="inlineStr"/>
@@ -12643,21 +12653,29 @@
     <row r="170">
       <c r="A170" s="14" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="C170" s="15" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C170" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D170" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="E170" s="15" t="inlineStr"/>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E170" s="15" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
+      </c>
       <c r="F170" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -12665,35 +12683,31 @@
       </c>
       <c r="G170" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H170" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H170" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I170" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J170" s="15" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="K170" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L170" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M170" s="15" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>8.75</v>
+      </c>
+      <c r="L170" s="15" t="inlineStr"/>
+      <c r="M170" s="15" t="inlineStr"/>
       <c r="N170" s="16" t="n">
-        <v>510.6</v>
-      </c>
-      <c r="O170" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O170" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P170" s="16" t="n">
@@ -12703,21 +12717,25 @@
     <row r="171">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>PSC-1228</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B171" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr"/>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
-        </is>
-      </c>
-      <c r="E171" s="12" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E171" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F171" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -12725,35 +12743,31 @@
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H171" s="12" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H171" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I171" s="12" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J171" s="12" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="K171" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L171" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-32829</t>
-        </is>
-      </c>
-      <c r="M171" s="12" t="inlineStr">
-        <is>
-          <t>00163534</t>
-        </is>
-      </c>
+        <v>1.75</v>
+      </c>
+      <c r="L171" s="12" t="inlineStr"/>
+      <c r="M171" s="12" t="inlineStr"/>
       <c r="N171" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="O171" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O171" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P171" s="13" t="n">
@@ -12763,18 +12777,18 @@
     <row r="172">
       <c r="A172" s="14" t="inlineStr">
         <is>
-          <t>PSC-1182</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C172" s="15" t="inlineStr"/>
       <c r="D172" s="15" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E172" s="15" t="inlineStr"/>
@@ -12785,27 +12799,35 @@
       </c>
       <c r="G172" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H172" s="15" t="inlineStr"/>
       <c r="I172" s="15" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J172" s="15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K172" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L172" s="15" t="inlineStr"/>
-      <c r="M172" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L172" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M172" s="15" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N172" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O172" s="16" t="n">
+        <v>510.6</v>
+      </c>
+      <c r="O172" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P172" s="16" t="n">
@@ -12815,18 +12837,18 @@
     <row r="173">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>PSC-1126</t>
+          <t>PSC-1228</t>
         </is>
       </c>
       <c r="B173" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARRY LE ROUET</t>
+          <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
       <c r="C173" s="12" t="inlineStr"/>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARRY LE ROUET</t>
+          <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
       <c r="E173" s="12" t="inlineStr"/>
@@ -12837,27 +12859,35 @@
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H173" s="12" t="inlineStr"/>
       <c r="I173" s="12" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="J173" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K173" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L173" s="12" t="inlineStr"/>
-      <c r="M173" s="12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L173" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-32829</t>
+        </is>
+      </c>
+      <c r="M173" s="12" t="inlineStr">
+        <is>
+          <t>00163534</t>
+        </is>
+      </c>
       <c r="N173" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O173" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="O173" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P173" s="13" t="n">
@@ -12867,18 +12897,18 @@
     <row r="174">
       <c r="A174" s="14" t="inlineStr">
         <is>
-          <t>PSC-1021</t>
+          <t>PSC-1182</t>
         </is>
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MELESSE</t>
+          <t>Commune de La Ville aux Dames</t>
         </is>
       </c>
       <c r="C174" s="15" t="inlineStr"/>
       <c r="D174" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MELESSE</t>
+          <t>Commune de La Ville aux Dames</t>
         </is>
       </c>
       <c r="E174" s="15" t="inlineStr"/>
@@ -12895,11 +12925,11 @@
       <c r="H174" s="15" t="inlineStr"/>
       <c r="I174" s="15" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J174" s="15" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K174" s="15" t="n">
         <v>0.5</v>
@@ -12919,18 +12949,18 @@
     <row r="175">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>PSC-589</t>
+          <t>PSC-1126</t>
         </is>
       </c>
       <c r="B175" s="12" t="inlineStr">
         <is>
-          <t>Mairie de Venelles</t>
+          <t>COMMUNE DE CARRY LE ROUET</t>
         </is>
       </c>
       <c r="C175" s="12" t="inlineStr"/>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>Mairie de Venelles</t>
+          <t>COMMUNE DE CARRY LE ROUET</t>
         </is>
       </c>
       <c r="E175" s="12" t="inlineStr"/>
@@ -12947,14 +12977,14 @@
       <c r="H175" s="12" t="inlineStr"/>
       <c r="I175" s="12" t="inlineStr">
         <is>
-          <t>20/03/2025</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="J175" s="12" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K175" s="12" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L175" s="12" t="inlineStr"/>
       <c r="M175" s="12" t="inlineStr"/>
@@ -12969,31 +12999,135 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="18" t="inlineStr">
+      <c r="A176" s="14" t="inlineStr">
+        <is>
+          <t>PSC-1021</t>
+        </is>
+      </c>
+      <c r="B176" s="15" t="inlineStr">
+        <is>
+          <t>MAIRIE DE MELESSE</t>
+        </is>
+      </c>
+      <c r="C176" s="15" t="inlineStr"/>
+      <c r="D176" s="15" t="inlineStr">
+        <is>
+          <t>MAIRIE DE MELESSE</t>
+        </is>
+      </c>
+      <c r="E176" s="15" t="inlineStr"/>
+      <c r="F176" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G176" s="15" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H176" s="15" t="inlineStr"/>
+      <c r="I176" s="15" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="J176" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="K176" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L176" s="15" t="inlineStr"/>
+      <c r="M176" s="15" t="inlineStr"/>
+      <c r="N176" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O176" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P176" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="11" t="inlineStr">
+        <is>
+          <t>PSC-589</t>
+        </is>
+      </c>
+      <c r="B177" s="12" t="inlineStr">
+        <is>
+          <t>Mairie de Venelles</t>
+        </is>
+      </c>
+      <c r="C177" s="12" t="inlineStr"/>
+      <c r="D177" s="12" t="inlineStr">
+        <is>
+          <t>Mairie de Venelles</t>
+        </is>
+      </c>
+      <c r="E177" s="12" t="inlineStr"/>
+      <c r="F177" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G177" s="12" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H177" s="12" t="inlineStr"/>
+      <c r="I177" s="12" t="inlineStr">
+        <is>
+          <t>20/03/2025</t>
+        </is>
+      </c>
+      <c r="J177" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="K177" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L177" s="12" t="inlineStr"/>
+      <c r="M177" s="12" t="inlineStr"/>
+      <c r="N177" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B176" s="18" t="inlineStr"/>
-      <c r="C176" s="18" t="inlineStr"/>
-      <c r="D176" s="18" t="inlineStr"/>
-      <c r="E176" s="18" t="inlineStr"/>
-      <c r="F176" s="18" t="inlineStr"/>
-      <c r="G176" s="18" t="inlineStr"/>
-      <c r="H176" s="18" t="inlineStr"/>
-      <c r="I176" s="18" t="inlineStr"/>
-      <c r="J176" s="18" t="inlineStr"/>
-      <c r="K176" s="18" t="inlineStr"/>
-      <c r="L176" s="18" t="inlineStr"/>
-      <c r="M176" s="18" t="inlineStr"/>
-      <c r="N176" s="19" t="n">
+      <c r="B178" s="18" t="inlineStr"/>
+      <c r="C178" s="18" t="inlineStr"/>
+      <c r="D178" s="18" t="inlineStr"/>
+      <c r="E178" s="18" t="inlineStr"/>
+      <c r="F178" s="18" t="inlineStr"/>
+      <c r="G178" s="18" t="inlineStr"/>
+      <c r="H178" s="18" t="inlineStr"/>
+      <c r="I178" s="18" t="inlineStr"/>
+      <c r="J178" s="18" t="inlineStr"/>
+      <c r="K178" s="18" t="inlineStr"/>
+      <c r="L178" s="18" t="inlineStr"/>
+      <c r="M178" s="18" t="inlineStr"/>
+      <c r="N178" s="19" t="n">
         <v>69305.66</v>
       </c>
-      <c r="O176" s="19" t="n">
+      <c r="O178" s="19" t="n">
         <v>34056.275</v>
       </c>
-      <c r="P176" s="19" t="n">
-        <v>143.24</v>
+      <c r="P178" s="19" t="n">
+        <v>140.73</v>
       </c>
     </row>
   </sheetData>
@@ -13170,6 +13304,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId169"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A175" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A176" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId173"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13927,16 +14063,16 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>125</v>
+        <v>128.5</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>31.75</v>
+        <v>32.25</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>3</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>159.75</v>
+        <v>163.75</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>43.5</v>
@@ -13946,7 +14082,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.7%</t>
         </is>
       </c>
     </row>
@@ -13957,7 +14093,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>69.5</v>
+        <v>69.75</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>6.25</v>
@@ -13966,7 +14102,7 @@
         <v>0.5</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>76.25</v>
+        <v>76.5</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>15</v>
@@ -13988,7 +14124,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>81.83</v>
+        <v>85.08</v>
       </c>
     </row>
   </sheetData>
@@ -14076,13 +14212,13 @@
         <v>389777</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>203845</v>
+        <v>202570</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>185931</v>
+        <v>187207</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>148625</v>
+        <v>149901</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>21917</v>
@@ -14101,13 +14237,13 @@
         <v>183883</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>78450</v>
+        <v>77174</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>105433</v>
+        <v>106709</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>91135</v>
+        <v>92411</v>
       </c>
       <c r="F6" s="26" t="n">
         <v>10060</v>

--- a/jira_export_2026-07-20.xlsx
+++ b/jira_export_2026-07-20.xlsx
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>389 h</t>
+          <t>400 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>74.8%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -909,7 +909,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>255</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -2238,7 +2238,7 @@
         <v>1</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>721.395</v>
       </c>
       <c r="P21" s="13" t="n">
-        <v>180.35</v>
+        <v>103.06</v>
       </c>
     </row>
     <row r="22">
@@ -4030,7 +4030,7 @@
         <v>2</v>
       </c>
       <c r="K46" s="15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L46" s="15" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>732.6</v>
       </c>
       <c r="P46" s="16" t="n">
-        <v>183.15</v>
+        <v>122.1</v>
       </c>
     </row>
     <row r="47">
@@ -4462,7 +4462,7 @@
         <v>2</v>
       </c>
       <c r="K52" s="15" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="L52" s="15" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>1028.4</v>
       </c>
       <c r="P52" s="16" t="n">
-        <v>342.8</v>
+        <v>293.83</v>
       </c>
     </row>
     <row r="53">
@@ -5534,7 +5534,7 @@
         <v>3</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="L67" s="12" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>1057.5</v>
       </c>
       <c r="P67" s="13" t="n">
-        <v>528.75</v>
+        <v>423</v>
       </c>
     </row>
     <row r="68">
@@ -9884,7 +9884,7 @@
         <v>10</v>
       </c>
       <c r="K128" s="15" t="n">
-        <v>3.12</v>
+        <v>3.62</v>
       </c>
       <c r="L128" s="15" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>10</v>
       </c>
       <c r="K129" s="12" t="n">
-        <v>3.12</v>
+        <v>3.62</v>
       </c>
       <c r="L129" s="12" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>17</v>
       </c>
       <c r="K150" s="15" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L150" s="15" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>19</v>
       </c>
       <c r="K155" s="12" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="L155" s="12" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>19</v>
       </c>
       <c r="K156" s="15" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="L156" s="15" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>34056.275</v>
       </c>
       <c r="P178" s="19" t="n">
-        <v>140.73</v>
+        <v>136.37</v>
       </c>
     </row>
   </sheetData>
@@ -13317,13 +13317,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="49" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
@@ -13343,7 +13343,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tickets 'Matériel GEODP' clôturés ce mois — 3 ligne(s)</t>
+          <t>Tickets 'Matériel GEODP' clôturés ce mois — 4 ligne(s)</t>
         </is>
       </c>
     </row>
@@ -13514,73 +13514,126 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-34147</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>[Mairie de Vaison la romaine] - Ajout d'une régie et mise en place de deux PAX</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Mairie de Vaison la romaine</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Ajout d'une régie et mise en place de deux PAX</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-34153</t>
+        </is>
+      </c>
+      <c r="J7" s="12" t="inlineStr">
+        <is>
+          <t>00171079</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
           <t>PDMDEP-33755</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>[COMMUNE DE MAINTENON] - Migration vers GeoDP V2</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>COMMUNE DE MAINTENON</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>Migration vers GeoDP V2</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>GEODP</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>Migration</t>
         </is>
       </c>
-      <c r="H7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="12" t="inlineStr">
+      <c r="H8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
         <is>
           <t>PDMDEP-33762</t>
         </is>
       </c>
-      <c r="J7" s="12" t="inlineStr">
+      <c r="J8" s="15" t="inlineStr">
         <is>
           <t>00169559</t>
         </is>
       </c>
-      <c r="K7" s="13" t="n">
+      <c r="K8" s="16" t="n">
         <v>815</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr"/>
-      <c r="C8" s="18" t="inlineStr"/>
-      <c r="D8" s="18" t="inlineStr"/>
-      <c r="E8" s="18" t="inlineStr"/>
-      <c r="F8" s="18" t="inlineStr"/>
-      <c r="G8" s="18" t="inlineStr"/>
-      <c r="H8" s="18" t="inlineStr"/>
-      <c r="I8" s="18" t="inlineStr"/>
-      <c r="J8" s="18" t="inlineStr"/>
-      <c r="K8" s="19" t="n">
-        <v>3260</v>
+      <c r="B9" s="18" t="inlineStr"/>
+      <c r="C9" s="18" t="inlineStr"/>
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr"/>
+      <c r="F9" s="18" t="inlineStr"/>
+      <c r="G9" s="18" t="inlineStr"/>
+      <c r="H9" s="18" t="inlineStr"/>
+      <c r="I9" s="18" t="inlineStr"/>
+      <c r="J9" s="18" t="inlineStr"/>
+      <c r="K9" s="19" t="n">
+        <v>4890</v>
       </c>
     </row>
   </sheetData>
@@ -13589,6 +13642,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14063,7 +14117,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>128.5</v>
+        <v>131.25</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>32.25</v>
@@ -14072,17 +14126,17 @@
         <v>3</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>163.75</v>
+        <v>166.5</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>43.5</v>
+        <v>45.75</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>486.15</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>34.2%</t>
         </is>
       </c>
     </row>
@@ -14093,7 +14147,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>69.75</v>
+        <v>74.75</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>6.25</v>
@@ -14102,7 +14156,7 @@
         <v>0.5</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>76.5</v>
+        <v>81.5</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>15</v>
@@ -14112,7 +14166,7 @@
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>30.9%</t>
         </is>
       </c>
     </row>
@@ -14124,7 +14178,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>85.08</v>
+        <v>86.08</v>
       </c>
     </row>
   </sheetData>
@@ -14288,17 +14342,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -14312,7 +14366,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 9 commande(s)</t>
+          <t>Épics créées ce mois — 10 commande(s)</t>
         </is>
       </c>
     </row>
@@ -14367,22 +14421,22 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34589</t>
+          <t>PDMDEP-34621</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34580</t>
+          <t>PDMDEP-34613</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE RIEZ</t>
+          <t>COMMUNE DE FORT-DE-FRANCE</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -14392,7 +14446,7 @@
       </c>
       <c r="F5" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -14402,7 +14456,7 @@
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>00176128</t>
+          <t>00176431</t>
         </is>
       </c>
       <c r="I5" s="26" t="n">
@@ -14412,34 +14466,34 @@
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34566</t>
+          <t>PDMDEP-34589</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34559</t>
+          <t>PDMDEP-34580</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
+          <t>COMMUNE DE RIEZ</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
           <t>Migration</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>Migration</t>
-        </is>
-      </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
           <t>Services</t>
@@ -14447,7 +14501,7 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>00154892</t>
+          <t>00176128</t>
         </is>
       </c>
       <c r="I6" s="27" t="n">
@@ -14457,22 +14511,22 @@
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34545</t>
+          <t>PDMDEP-34566</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34537</t>
+          <t>PDMDEP-34559</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRON</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -14482,7 +14536,7 @@
       </c>
       <c r="F7" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
@@ -14492,32 +14546,32 @@
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>00173172</t>
+          <t>00154892</t>
         </is>
       </c>
       <c r="I7" s="26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34527</t>
+          <t>PDMDEP-34545</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34521</t>
+          <t>PDMDEP-34537</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE FRONTON</t>
+          <t>COMMUNE DE BRON</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -14537,32 +14591,32 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>00173007</t>
+          <t>00173172</t>
         </is>
       </c>
       <c r="I8" s="27" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34481</t>
+          <t>PDMDEP-34527</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34475</t>
+          <t>PDMDEP-34521</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>Mairie de Pontcharra</t>
+          <t>COMMUNE DE FRONTON</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -14572,7 +14626,7 @@
       </c>
       <c r="F9" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G9" s="15" t="inlineStr">
@@ -14582,22 +14636,22 @@
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>00172611</t>
+          <t>00173007</t>
         </is>
       </c>
       <c r="I9" s="26" t="n">
-        <v>1050</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34466</t>
+          <t>PDMDEP-34481</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34457</t>
+          <t>PDMDEP-34475</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -14607,7 +14661,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Commune de La Flèche</t>
+          <t>Mairie de Pontcharra</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -14627,32 +14681,32 @@
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>00172594</t>
+          <t>00172611</t>
         </is>
       </c>
       <c r="I10" s="27" t="n">
-        <v>4475</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34420</t>
+          <t>PDMDEP-34466</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34411</t>
+          <t>PDMDEP-34457</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MAIZIERES LES METZ</t>
+          <t>Commune de La Flèche</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -14672,32 +14726,32 @@
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>00172317</t>
+          <t>00172594</t>
         </is>
       </c>
       <c r="I11" s="26" t="n">
-        <v>2035</v>
+        <v>4475</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34396</t>
+          <t>PDMDEP-34420</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34390</t>
+          <t>PDMDEP-34411</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Commune Le THOR</t>
+          <t>MAIRIE DE MAIZIERES LES METZ</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
@@ -14707,7 +14761,7 @@
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
@@ -14717,83 +14771,107 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>00171793</t>
+          <t>00172317</t>
         </is>
       </c>
       <c r="I12" s="27" t="n">
-        <v>250</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
+          <t>PDMDEP-34396</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34390</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Commune Le THOR</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>00171793</t>
+        </is>
+      </c>
+      <c r="I13" s="26" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
           <t>PDMDEP-34499</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>PDMDEP-34495</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>COMMUNE DE CLICHY</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G13" s="15" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H13" s="15" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>00172678</t>
         </is>
       </c>
-      <c r="I13" s="26" t="n">
+      <c r="I14" s="27" t="n">
         <v>4300</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="n"/>
-      <c r="C14" s="18" t="n"/>
-      <c r="D14" s="18" t="n"/>
-      <c r="E14" s="18" t="n"/>
-      <c r="F14" s="18" t="n"/>
-      <c r="G14" s="18" t="n"/>
-      <c r="H14" s="18" t="inlineStr">
-        <is>
-          <t>9 commande(s)</t>
-        </is>
-      </c>
-      <c r="I14" s="25" t="n">
-        <v>13610</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B15" s="18" t="n"/>
@@ -14804,17 +14882,17 @@
       <c r="G15" s="18" t="n"/>
       <c r="H15" s="18" t="inlineStr">
         <is>
-          <t>1 commande(s)</t>
+          <t>10 commande(s)</t>
         </is>
       </c>
       <c r="I15" s="25" t="n">
-        <v>4300</v>
+        <v>13610</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B16" s="18" t="n"/>
@@ -14825,10 +14903,31 @@
       <c r="G16" s="18" t="n"/>
       <c r="H16" s="18" t="inlineStr">
         <is>
-          <t>8 commande(s)</t>
+          <t>1 commande(s)</t>
         </is>
       </c>
       <c r="I16" s="25" t="n">
+        <v>4300</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="n"/>
+      <c r="C17" s="18" t="n"/>
+      <c r="D17" s="18" t="n"/>
+      <c r="E17" s="18" t="n"/>
+      <c r="F17" s="18" t="n"/>
+      <c r="G17" s="18" t="n"/>
+      <c r="H17" s="18" t="inlineStr">
+        <is>
+          <t>9 commande(s)</t>
+        </is>
+      </c>
+      <c r="I17" s="25" t="n">
         <v>9310</v>
       </c>
     </row>

--- a/jira_export_2026-07-20.xlsx
+++ b/jira_export_2026-07-20.xlsx
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>400 h</t>
+          <t>406 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>78.2%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -3238,7 +3238,7 @@
         <v>1</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>532.4</v>
       </c>
       <c r="P35" s="13" t="n">
-        <v>101.41</v>
+        <v>85.18000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -5534,7 +5534,7 @@
         <v>3</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="L67" s="12" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>1057.5</v>
       </c>
       <c r="P67" s="13" t="n">
-        <v>423</v>
+        <v>384.55</v>
       </c>
     </row>
     <row r="68">
@@ -8406,7 +8406,7 @@
         <v>6</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="L107" s="12" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>6</v>
       </c>
       <c r="K108" s="15" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>6</v>
       </c>
       <c r="K109" s="12" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="L109" s="12" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>11</v>
       </c>
       <c r="K130" s="15" t="n">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
       <c r="L130" s="15" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>15</v>
       </c>
       <c r="K145" s="12" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="L145" s="12" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>19</v>
       </c>
       <c r="K155" s="12" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="L155" s="12" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>19</v>
       </c>
       <c r="K156" s="15" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="L156" s="15" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>34056.275</v>
       </c>
       <c r="P178" s="19" t="n">
-        <v>136.37</v>
+        <v>134.47</v>
       </c>
     </row>
   </sheetData>
@@ -14117,7 +14117,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>131.25</v>
+        <v>134.75</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>32.25</v>
@@ -14126,7 +14126,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>166.5</v>
+        <v>170</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>45.75</v>
@@ -14136,7 +14136,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>35.0%</t>
         </is>
       </c>
     </row>
@@ -14159,7 +14159,7 @@
         <v>81.5</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>15</v>
+        <v>15.75</v>
       </c>
       <c r="G6" s="12" t="n">
         <v>263.34</v>
@@ -14178,7 +14178,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>86.08</v>
+        <v>88.08</v>
       </c>
     </row>
   </sheetData>
